--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_paper_forest_products.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0799307660262332</v>
+        <v>0.07980690449418072</v>
       </c>
       <c r="C2">
-        <v>758.1868622833457</v>
+        <v>753.2031845180471</v>
       </c>
       <c r="D2">
-        <v>752.0968622833457</v>
+        <v>754.836184518047</v>
       </c>
       <c r="E2">
-        <v>-133.5</v>
+        <v>-125.777</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.723</v>
       </c>
       <c r="G2">
         <v>6.09</v>
@@ -1573,28 +1573,28 @@
         <v>49.35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3884668999999999</v>
       </c>
       <c r="N2">
-        <v>49.35</v>
+        <v>48.9615331</v>
       </c>
       <c r="O2">
-        <v>9.870000000000001</v>
+        <v>9.792306620000002</v>
       </c>
       <c r="P2">
-        <v>39.48</v>
+        <v>39.16922648000001</v>
       </c>
       <c r="Q2">
-        <v>53.38</v>
+        <v>53.06922648</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0799307660262332</v>
+        <v>0.08020657019614215</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6706480940382392</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>127.0378505864979</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07980690449418072</v>
+        <v>0.07968304296212825</v>
       </c>
       <c r="C3">
-        <v>753.2031845180471</v>
+        <v>748.2395342720686</v>
       </c>
       <c r="D3">
-        <v>754.836184518047</v>
+        <v>757.5955342720686</v>
       </c>
       <c r="E3">
-        <v>-125.777</v>
+        <v>-118.054</v>
       </c>
       <c r="F3">
-        <v>7.723</v>
+        <v>15.446</v>
       </c>
       <c r="G3">
         <v>6.09</v>
@@ -1655,28 +1655,28 @@
         <v>49.35</v>
       </c>
       <c r="M3">
-        <v>0.3884668999999999</v>
+        <v>0.7769337999999999</v>
       </c>
       <c r="N3">
-        <v>48.9615331</v>
+        <v>48.5730662</v>
       </c>
       <c r="O3">
-        <v>9.792306620000002</v>
+        <v>9.71461324</v>
       </c>
       <c r="P3">
-        <v>39.16922648000001</v>
+        <v>38.85845296</v>
       </c>
       <c r="Q3">
-        <v>53.06922648</v>
+        <v>52.75845296</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08020657019614215</v>
+        <v>0.08048800302257986</v>
       </c>
       <c r="T3">
-        <v>0.6706480940382392</v>
+        <v>0.6761337436561545</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>127.0378505864979</v>
+        <v>63.51892529324893</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07968304296212825</v>
+        <v>0.07955918143007579</v>
       </c>
       <c r="C4">
-        <v>748.2395342720686</v>
+        <v>743.2961319867053</v>
       </c>
       <c r="D4">
-        <v>757.5955342720686</v>
+        <v>760.3751319867052</v>
       </c>
       <c r="E4">
-        <v>-118.054</v>
+        <v>-110.331</v>
       </c>
       <c r="F4">
-        <v>15.446</v>
+        <v>23.169</v>
       </c>
       <c r="G4">
         <v>6.09</v>
@@ -1737,28 +1737,28 @@
         <v>49.35</v>
       </c>
       <c r="M4">
-        <v>0.7769337999999999</v>
+        <v>1.1654007</v>
       </c>
       <c r="N4">
-        <v>48.5730662</v>
+        <v>48.1845993</v>
       </c>
       <c r="O4">
-        <v>9.71461324</v>
+        <v>9.636919860000001</v>
       </c>
       <c r="P4">
-        <v>38.85845296</v>
+        <v>38.54767944</v>
       </c>
       <c r="Q4">
-        <v>52.75845296</v>
+        <v>52.44767944</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08048800302257986</v>
+        <v>0.08077523858770699</v>
       </c>
       <c r="T4">
-        <v>0.6761337436561545</v>
+        <v>0.6817324994517588</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.51892529324893</v>
+        <v>42.34595019549929</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07955918143007579</v>
+        <v>0.07943531989802333</v>
       </c>
       <c r="C5">
-        <v>743.2961319867053</v>
+        <v>738.3732013503386</v>
       </c>
       <c r="D5">
-        <v>760.3751319867052</v>
+        <v>763.1752013503386</v>
       </c>
       <c r="E5">
-        <v>-110.331</v>
+        <v>-102.608</v>
       </c>
       <c r="F5">
-        <v>23.169</v>
+        <v>30.892</v>
       </c>
       <c r="G5">
         <v>6.09</v>
@@ -1819,28 +1819,28 @@
         <v>49.35</v>
       </c>
       <c r="M5">
-        <v>1.1654007</v>
+        <v>1.5538676</v>
       </c>
       <c r="N5">
-        <v>48.1845993</v>
+        <v>47.7961324</v>
       </c>
       <c r="O5">
-        <v>9.636919860000001</v>
+        <v>9.559226480000001</v>
       </c>
       <c r="P5">
-        <v>38.54767944</v>
+        <v>38.23690592000001</v>
       </c>
       <c r="Q5">
-        <v>52.44767944</v>
+        <v>52.13690592</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08077523858770699</v>
+        <v>0.08106845822710763</v>
       </c>
       <c r="T5">
-        <v>0.6817324994517588</v>
+        <v>0.687447895993105</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.34595019549929</v>
+        <v>31.75946264662447</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07943531989802333</v>
+        <v>0.07931145836597085</v>
       </c>
       <c r="C6">
-        <v>738.3732013503386</v>
+        <v>733.4709693584447</v>
       </c>
       <c r="D6">
-        <v>763.1752013503386</v>
+        <v>765.9959693584447</v>
       </c>
       <c r="E6">
-        <v>-102.608</v>
+        <v>-94.88499999999999</v>
       </c>
       <c r="F6">
-        <v>30.892</v>
+        <v>38.615</v>
       </c>
       <c r="G6">
         <v>6.09</v>
@@ -1901,28 +1901,28 @@
         <v>49.35</v>
       </c>
       <c r="M6">
-        <v>1.5538676</v>
+        <v>1.9423345</v>
       </c>
       <c r="N6">
-        <v>47.7961324</v>
+        <v>47.4076655</v>
       </c>
       <c r="O6">
-        <v>9.559226480000001</v>
+        <v>9.4815331</v>
       </c>
       <c r="P6">
-        <v>38.23690592000001</v>
+        <v>37.9261324</v>
       </c>
       <c r="Q6">
-        <v>52.13690592</v>
+        <v>51.8261324</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08106845822710763</v>
+        <v>0.08136785091154827</v>
       </c>
       <c r="T6">
-        <v>0.687447895993105</v>
+        <v>0.6932836166721635</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.75946264662447</v>
+        <v>25.40757011729957</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07931145836597085</v>
+        <v>0.07918759683391841</v>
       </c>
       <c r="C7">
-        <v>733.4709693584447</v>
+        <v>728.5896663749353</v>
       </c>
       <c r="D7">
-        <v>765.9959693584447</v>
+        <v>768.8376663749352</v>
       </c>
       <c r="E7">
-        <v>-94.88499999999999</v>
+        <v>-87.16200000000001</v>
       </c>
       <c r="F7">
-        <v>38.615</v>
+        <v>46.338</v>
       </c>
       <c r="G7">
         <v>6.09</v>
@@ -1983,28 +1983,28 @@
         <v>49.35</v>
       </c>
       <c r="M7">
-        <v>1.9423345</v>
+        <v>2.3308014</v>
       </c>
       <c r="N7">
-        <v>47.4076655</v>
+        <v>47.0191986</v>
       </c>
       <c r="O7">
-        <v>9.4815331</v>
+        <v>9.403839720000001</v>
       </c>
       <c r="P7">
-        <v>37.9261324</v>
+        <v>37.61535888</v>
       </c>
       <c r="Q7">
-        <v>51.8261324</v>
+        <v>51.51535888</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08136785091154827</v>
+        <v>0.08167361365310469</v>
       </c>
       <c r="T7">
-        <v>0.6932836166721635</v>
+        <v>0.6992435016209895</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.40757011729957</v>
+        <v>21.17297509774964</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07918759683391841</v>
+        <v>0.07906373530186593</v>
       </c>
       <c r="C8">
-        <v>728.5896663749353</v>
+        <v>723.7295261948758</v>
       </c>
       <c r="D8">
-        <v>768.8376663749352</v>
+        <v>771.7005261948758</v>
       </c>
       <c r="E8">
-        <v>-87.16200000000001</v>
+        <v>-79.43900000000001</v>
       </c>
       <c r="F8">
-        <v>46.33799999999999</v>
+        <v>54.06099999999999</v>
       </c>
       <c r="G8">
         <v>6.09</v>
@@ -2065,28 +2065,28 @@
         <v>49.35</v>
       </c>
       <c r="M8">
-        <v>2.330801399999999</v>
+        <v>2.7192683</v>
       </c>
       <c r="N8">
-        <v>47.0191986</v>
+        <v>46.6307317</v>
       </c>
       <c r="O8">
-        <v>9.403839720000001</v>
+        <v>9.326146339999999</v>
       </c>
       <c r="P8">
-        <v>37.61535888</v>
+        <v>37.30458536</v>
       </c>
       <c r="Q8">
-        <v>51.51535888</v>
+        <v>51.20458536</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08167361365310469</v>
+        <v>0.08198595193749025</v>
       </c>
       <c r="T8">
-        <v>0.6992435016209895</v>
+        <v>0.7053315561386072</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.17297509774965</v>
+        <v>18.1482643694997</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07906373530186593</v>
+        <v>0.07893987376981347</v>
       </c>
       <c r="C9">
-        <v>723.7295261948758</v>
+        <v>718.890786108601</v>
       </c>
       <c r="D9">
-        <v>771.7005261948758</v>
+        <v>774.584786108601</v>
       </c>
       <c r="E9">
-        <v>-79.43899999999999</v>
+        <v>-71.71600000000001</v>
       </c>
       <c r="F9">
-        <v>54.061</v>
+        <v>61.784</v>
       </c>
       <c r="G9">
         <v>6.09</v>
@@ -2147,28 +2147,28 @@
         <v>49.35</v>
       </c>
       <c r="M9">
-        <v>2.7192683</v>
+        <v>3.1077352</v>
       </c>
       <c r="N9">
-        <v>46.6307317</v>
+        <v>46.2422648</v>
       </c>
       <c r="O9">
-        <v>9.326146339999999</v>
+        <v>9.24845296</v>
       </c>
       <c r="P9">
-        <v>37.30458536</v>
+        <v>36.99381184</v>
       </c>
       <c r="Q9">
-        <v>51.20458536</v>
+        <v>50.89381184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08198595193749025</v>
+        <v>0.08230508018457985</v>
       </c>
       <c r="T9">
-        <v>0.7053315561386072</v>
+        <v>0.7115519596674775</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.14826436949969</v>
+        <v>15.87973132331223</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07893987376981347</v>
+        <v>0.078816012237761</v>
       </c>
       <c r="C10">
-        <v>718.890786108601</v>
+        <v>714.0736869672826</v>
       </c>
       <c r="D10">
-        <v>774.584786108601</v>
+        <v>777.4906869672825</v>
       </c>
       <c r="E10">
-        <v>-71.71600000000001</v>
+        <v>-63.99300000000001</v>
       </c>
       <c r="F10">
-        <v>61.784</v>
+        <v>69.50699999999999</v>
       </c>
       <c r="G10">
         <v>6.09</v>
@@ -2229,28 +2229,28 @@
         <v>49.35</v>
       </c>
       <c r="M10">
-        <v>3.1077352</v>
+        <v>3.496202099999999</v>
       </c>
       <c r="N10">
-        <v>46.2422648</v>
+        <v>45.8537979</v>
       </c>
       <c r="O10">
-        <v>9.24845296</v>
+        <v>9.17075958</v>
       </c>
       <c r="P10">
-        <v>36.99381184</v>
+        <v>36.68303832</v>
       </c>
       <c r="Q10">
-        <v>50.89381184</v>
+        <v>50.58303832</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08230508018457985</v>
+        <v>0.08263122223929779</v>
       </c>
       <c r="T10">
-        <v>0.7115519596674775</v>
+        <v>0.7179090753618175</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.87973132331223</v>
+        <v>14.1153167318331</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.078816012237761</v>
+        <v>0.07881215070570852</v>
       </c>
       <c r="C11">
-        <v>714.0736869672826</v>
+        <v>706.441632426577</v>
       </c>
       <c r="D11">
-        <v>777.4906869672825</v>
+        <v>777.581632426577</v>
       </c>
       <c r="E11">
-        <v>-63.99300000000001</v>
+        <v>-56.27000000000001</v>
       </c>
       <c r="F11">
-        <v>69.50699999999999</v>
+        <v>77.22999999999999</v>
       </c>
       <c r="G11">
         <v>6.09</v>
@@ -2311,45 +2311,45 @@
         <v>49.35</v>
       </c>
       <c r="M11">
-        <v>3.496202099999999</v>
+        <v>4.000513999999999</v>
       </c>
       <c r="N11">
-        <v>45.8537979</v>
+        <v>45.349486</v>
       </c>
       <c r="O11">
-        <v>9.17075958</v>
+        <v>9.0698972</v>
       </c>
       <c r="P11">
-        <v>36.68303832</v>
+        <v>36.2795888</v>
       </c>
       <c r="Q11">
-        <v>50.58303832</v>
+        <v>50.1795888</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08263122223929779</v>
+        <v>0.08296461189523169</v>
       </c>
       <c r="T11">
-        <v>0.7179090753618175</v>
+        <v>0.7244074602938094</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.1153167318331</v>
+        <v>12.33591483494371</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07881215070570853</v>
+        <v>0.07870028917365607</v>
       </c>
       <c r="C12">
-        <v>706.4416324265767</v>
+        <v>701.3624229489025</v>
       </c>
       <c r="D12">
-        <v>777.5816324265767</v>
+        <v>780.2254229489024</v>
       </c>
       <c r="E12">
-        <v>-56.27</v>
+        <v>-48.54700000000001</v>
       </c>
       <c r="F12">
-        <v>77.23</v>
+        <v>84.95299999999999</v>
       </c>
       <c r="G12">
         <v>6.09</v>
@@ -2393,28 +2393,28 @@
         <v>49.35</v>
       </c>
       <c r="M12">
-        <v>4.000514</v>
+        <v>4.4005654</v>
       </c>
       <c r="N12">
-        <v>45.349486</v>
+        <v>44.9494346</v>
       </c>
       <c r="O12">
-        <v>9.0698972</v>
+        <v>8.989886920000002</v>
       </c>
       <c r="P12">
-        <v>36.2795888</v>
+        <v>35.95954768</v>
       </c>
       <c r="Q12">
-        <v>50.1795888</v>
+        <v>49.85954768</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0829646118952317</v>
+        <v>0.08330549345354614</v>
       </c>
       <c r="T12">
-        <v>0.7244074602938095</v>
+        <v>0.7310518763478687</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.33591483494371</v>
+        <v>11.21446803176701</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07870028917365607</v>
+        <v>0.07858842764160361</v>
       </c>
       <c r="C13">
-        <v>701.3624229489025</v>
+        <v>696.3012526685625</v>
       </c>
       <c r="D13">
-        <v>780.2254229489024</v>
+        <v>782.8872526685625</v>
       </c>
       <c r="E13">
-        <v>-48.54700000000001</v>
+        <v>-40.82400000000001</v>
       </c>
       <c r="F13">
-        <v>84.95299999999999</v>
+        <v>92.67599999999999</v>
       </c>
       <c r="G13">
         <v>6.09</v>
@@ -2475,28 +2475,28 @@
         <v>49.35</v>
       </c>
       <c r="M13">
-        <v>4.4005654</v>
+        <v>4.800616799999999</v>
       </c>
       <c r="N13">
-        <v>44.9494346</v>
+        <v>44.5493832</v>
       </c>
       <c r="O13">
-        <v>8.989886920000002</v>
+        <v>8.90987664</v>
       </c>
       <c r="P13">
-        <v>35.95954768</v>
+        <v>35.63950656</v>
       </c>
       <c r="Q13">
-        <v>49.85954768</v>
+        <v>49.53950656</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08330549345354614</v>
+        <v>0.08365412232000409</v>
       </c>
       <c r="T13">
-        <v>0.7310518763478687</v>
+        <v>0.7378473018577021</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.21446803176701</v>
+        <v>10.27992902911976</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07858842764160361</v>
+        <v>0.07865336610955112</v>
       </c>
       <c r="C14">
-        <v>696.3012526685625</v>
+        <v>687.0307857029431</v>
       </c>
       <c r="D14">
-        <v>782.8872526685625</v>
+        <v>781.3397857029431</v>
       </c>
       <c r="E14">
-        <v>-40.82400000000001</v>
+        <v>-33.101</v>
       </c>
       <c r="F14">
-        <v>92.67599999999999</v>
+        <v>100.399</v>
       </c>
       <c r="G14">
         <v>6.09</v>
@@ -2557,45 +2557,45 @@
         <v>49.35</v>
       </c>
       <c r="M14">
-        <v>4.800616799999999</v>
+        <v>5.3713465</v>
       </c>
       <c r="N14">
-        <v>44.5493832</v>
+        <v>43.9786535</v>
       </c>
       <c r="O14">
-        <v>8.90987664</v>
+        <v>8.7957307</v>
       </c>
       <c r="P14">
-        <v>35.63950656</v>
+        <v>35.1829228</v>
       </c>
       <c r="Q14">
-        <v>49.53950656</v>
+        <v>49.0829228</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08365412232000409</v>
+        <v>0.08401076564316221</v>
       </c>
       <c r="T14">
-        <v>0.7378473018577021</v>
+        <v>0.7447989440459223</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.27992902911976</v>
+        <v>9.187640380303153</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07865336610955112</v>
+        <v>0.07855510457749865</v>
       </c>
       <c r="C15">
-        <v>687.0307857029431</v>
+        <v>681.6517148519121</v>
       </c>
       <c r="D15">
-        <v>781.3397857029431</v>
+        <v>783.683714851912</v>
       </c>
       <c r="E15">
-        <v>-33.101</v>
+        <v>-25.378</v>
       </c>
       <c r="F15">
-        <v>100.399</v>
+        <v>108.122</v>
       </c>
       <c r="G15">
         <v>6.09</v>
@@ -2639,28 +2639,28 @@
         <v>49.35</v>
       </c>
       <c r="M15">
-        <v>5.3713465</v>
+        <v>5.784527</v>
       </c>
       <c r="N15">
-        <v>43.9786535</v>
+        <v>43.565473</v>
       </c>
       <c r="O15">
-        <v>8.7957307</v>
+        <v>8.713094600000002</v>
       </c>
       <c r="P15">
-        <v>35.1829228</v>
+        <v>34.85237840000001</v>
       </c>
       <c r="Q15">
-        <v>49.0829228</v>
+        <v>48.7523784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08401076564316221</v>
+        <v>0.08437570299709146</v>
       </c>
       <c r="T15">
-        <v>0.7447989440459223</v>
+        <v>0.7519122523315431</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.187640380303153</v>
+        <v>8.531380353138641</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07855510457749865</v>
+        <v>0.07845684304544619</v>
       </c>
       <c r="C16">
-        <v>681.6517148519121</v>
+        <v>676.286749348962</v>
       </c>
       <c r="D16">
-        <v>783.683714851912</v>
+        <v>786.041749348962</v>
       </c>
       <c r="E16">
-        <v>-25.378</v>
+        <v>-17.65499999999999</v>
       </c>
       <c r="F16">
-        <v>108.122</v>
+        <v>115.845</v>
       </c>
       <c r="G16">
         <v>6.09</v>
@@ -2721,28 +2721,28 @@
         <v>49.35</v>
       </c>
       <c r="M16">
-        <v>5.784527</v>
+        <v>6.197707500000001</v>
       </c>
       <c r="N16">
-        <v>43.565473</v>
+        <v>43.1522925</v>
       </c>
       <c r="O16">
-        <v>8.713094600000002</v>
+        <v>8.630458500000001</v>
       </c>
       <c r="P16">
-        <v>34.85237840000001</v>
+        <v>34.521834</v>
       </c>
       <c r="Q16">
-        <v>48.7523784</v>
+        <v>48.421834</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08437570299709146</v>
+        <v>0.08474922711228963</v>
       </c>
       <c r="T16">
-        <v>0.7519122523315431</v>
+        <v>0.7591929325768255</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.531380353138641</v>
+        <v>7.962621662929397</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07845684304544619</v>
+        <v>0.07846098151339373</v>
       </c>
       <c r="C17">
-        <v>676.286749348962</v>
+        <v>668.4641501197173</v>
       </c>
       <c r="D17">
-        <v>786.041749348962</v>
+        <v>785.9421501197172</v>
       </c>
       <c r="E17">
-        <v>-17.65500000000002</v>
+        <v>-9.932000000000002</v>
       </c>
       <c r="F17">
-        <v>115.845</v>
+        <v>123.568</v>
       </c>
       <c r="G17">
         <v>6.09</v>
@@ -2803,45 +2803,45 @@
         <v>49.35</v>
       </c>
       <c r="M17">
-        <v>6.197707499999999</v>
+        <v>6.7097424</v>
       </c>
       <c r="N17">
-        <v>43.1522925</v>
+        <v>42.6402576</v>
       </c>
       <c r="O17">
-        <v>8.630458500000001</v>
+        <v>8.52805152</v>
       </c>
       <c r="P17">
-        <v>34.521834</v>
+        <v>34.11220608</v>
       </c>
       <c r="Q17">
-        <v>48.421834</v>
+        <v>48.01220608</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08474922711228963</v>
+        <v>0.08513164465880206</v>
       </c>
       <c r="T17">
-        <v>0.7591929325768255</v>
+        <v>0.7666469623517576</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.962621662929399</v>
+        <v>7.354976846801153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07846098151339373</v>
+        <v>0.07836911998134126</v>
       </c>
       <c r="C18">
-        <v>668.4641501197173</v>
+        <v>662.9579078968993</v>
       </c>
       <c r="D18">
-        <v>785.9421501197172</v>
+        <v>788.1589078968992</v>
       </c>
       <c r="E18">
-        <v>-9.932000000000002</v>
+        <v>-2.209000000000003</v>
       </c>
       <c r="F18">
-        <v>123.568</v>
+        <v>131.291</v>
       </c>
       <c r="G18">
         <v>6.09</v>
@@ -2885,28 +2885,28 @@
         <v>49.35</v>
       </c>
       <c r="M18">
-        <v>6.7097424</v>
+        <v>7.1291013</v>
       </c>
       <c r="N18">
-        <v>42.6402576</v>
+        <v>42.2208987</v>
       </c>
       <c r="O18">
-        <v>8.52805152</v>
+        <v>8.444179740000001</v>
       </c>
       <c r="P18">
-        <v>34.11220608</v>
+        <v>33.77671896</v>
       </c>
       <c r="Q18">
-        <v>48.01220608</v>
+        <v>47.67671896</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08513164465880206</v>
+        <v>0.08552327708595334</v>
       </c>
       <c r="T18">
-        <v>0.7666469623517576</v>
+        <v>0.7742806073019891</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.354976846801153</v>
+        <v>6.922331149930496</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07836911998134126</v>
+        <v>0.07827725844928879</v>
       </c>
       <c r="C19">
-        <v>662.9579078968993</v>
+        <v>657.4642058191133</v>
       </c>
       <c r="D19">
-        <v>788.1589078968992</v>
+        <v>790.3882058191133</v>
       </c>
       <c r="E19">
-        <v>-2.209000000000003</v>
+        <v>5.51400000000001</v>
       </c>
       <c r="F19">
-        <v>131.291</v>
+        <v>139.014</v>
       </c>
       <c r="G19">
         <v>6.09</v>
@@ -2967,28 +2967,28 @@
         <v>49.35</v>
       </c>
       <c r="M19">
-        <v>7.1291013</v>
+        <v>7.548460200000001</v>
       </c>
       <c r="N19">
-        <v>42.2208987</v>
+        <v>41.8015398</v>
       </c>
       <c r="O19">
-        <v>8.444179740000001</v>
+        <v>8.36030796</v>
       </c>
       <c r="P19">
-        <v>33.77671896</v>
+        <v>33.44123184</v>
       </c>
       <c r="Q19">
-        <v>47.67671896</v>
+        <v>47.34123184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08552327708595334</v>
+        <v>0.08592446152352293</v>
       </c>
       <c r="T19">
-        <v>0.7742806073019891</v>
+        <v>0.7821004387144216</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.922331149930496</v>
+        <v>6.53775719715658</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0782772584492888</v>
+        <v>0.07818539691723635</v>
       </c>
       <c r="C20">
-        <v>657.464205819113</v>
+        <v>651.9831505971341</v>
       </c>
       <c r="D20">
-        <v>790.388205819113</v>
+        <v>792.630150597134</v>
       </c>
       <c r="E20">
-        <v>5.513999999999982</v>
+        <v>13.23699999999999</v>
       </c>
       <c r="F20">
-        <v>139.014</v>
+        <v>146.737</v>
       </c>
       <c r="G20">
         <v>6.09</v>
@@ -3049,28 +3049,28 @@
         <v>49.35</v>
       </c>
       <c r="M20">
-        <v>7.548460199999999</v>
+        <v>7.9678191</v>
       </c>
       <c r="N20">
-        <v>41.8015398</v>
+        <v>41.3821809</v>
       </c>
       <c r="O20">
-        <v>8.36030796</v>
+        <v>8.276436180000001</v>
       </c>
       <c r="P20">
-        <v>33.44123184</v>
+        <v>33.10574472</v>
       </c>
       <c r="Q20">
-        <v>47.34123184</v>
+        <v>47.00574472</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08592446152352293</v>
+        <v>0.0863355517496745</v>
       </c>
       <c r="T20">
-        <v>0.7821004387144215</v>
+        <v>0.7901133523839511</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.537757197156581</v>
+        <v>6.193664713095708</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07818539691723635</v>
+        <v>0.07825353538518386</v>
       </c>
       <c r="C21">
-        <v>651.9831505971341</v>
+        <v>642.5959681446006</v>
       </c>
       <c r="D21">
-        <v>792.630150597134</v>
+        <v>790.9659681446007</v>
       </c>
       <c r="E21">
-        <v>13.23699999999999</v>
+        <v>20.96000000000001</v>
       </c>
       <c r="F21">
-        <v>146.737</v>
+        <v>154.46</v>
       </c>
       <c r="G21">
         <v>6.09</v>
@@ -3131,45 +3131,45 @@
         <v>49.35</v>
       </c>
       <c r="M21">
-        <v>7.9678191</v>
+        <v>8.541638000000001</v>
       </c>
       <c r="N21">
-        <v>41.3821809</v>
+        <v>40.808362</v>
       </c>
       <c r="O21">
-        <v>8.276436180000001</v>
+        <v>8.1616724</v>
       </c>
       <c r="P21">
-        <v>33.10574472</v>
+        <v>32.6466896</v>
       </c>
       <c r="Q21">
-        <v>47.00574472</v>
+        <v>46.5466896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0863355517496745</v>
+        <v>0.08675691923147982</v>
       </c>
       <c r="T21">
-        <v>0.7901133523839511</v>
+        <v>0.7983265888952186</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.193664713095708</v>
+        <v>5.777580365733129</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07825353538518386</v>
+        <v>0.07816967385313141</v>
       </c>
       <c r="C22">
-        <v>642.5959681446006</v>
+        <v>636.9221583276997</v>
       </c>
       <c r="D22">
-        <v>790.9659681446007</v>
+        <v>793.0151583276996</v>
       </c>
       <c r="E22">
-        <v>20.96000000000001</v>
+        <v>28.68299999999999</v>
       </c>
       <c r="F22">
-        <v>154.46</v>
+        <v>162.183</v>
       </c>
       <c r="G22">
         <v>6.09</v>
@@ -3213,28 +3213,28 @@
         <v>49.35</v>
       </c>
       <c r="M22">
-        <v>8.541638000000001</v>
+        <v>8.9687199</v>
       </c>
       <c r="N22">
-        <v>40.808362</v>
+        <v>40.3812801</v>
       </c>
       <c r="O22">
-        <v>8.1616724</v>
+        <v>8.076256020000001</v>
       </c>
       <c r="P22">
-        <v>32.6466896</v>
+        <v>32.30502408</v>
       </c>
       <c r="Q22">
-        <v>46.5466896</v>
+        <v>46.20502407999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08675691923147982</v>
+        <v>0.08718895424447012</v>
       </c>
       <c r="T22">
-        <v>0.7983265888952186</v>
+        <v>0.8067477554447463</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.777580365733129</v>
+        <v>5.502457491174409</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07816967385313141</v>
+        <v>0.07808581232107893</v>
       </c>
       <c r="C23">
-        <v>636.9221583276997</v>
+        <v>631.2589939439398</v>
       </c>
       <c r="D23">
-        <v>793.0151583276996</v>
+        <v>795.0749939439397</v>
       </c>
       <c r="E23">
-        <v>28.68299999999999</v>
+        <v>36.40599999999998</v>
       </c>
       <c r="F23">
-        <v>162.183</v>
+        <v>169.906</v>
       </c>
       <c r="G23">
         <v>6.09</v>
@@ -3295,28 +3295,28 @@
         <v>49.35</v>
       </c>
       <c r="M23">
-        <v>8.9687199</v>
+        <v>9.395801799999999</v>
       </c>
       <c r="N23">
-        <v>40.3812801</v>
+        <v>39.9541982</v>
       </c>
       <c r="O23">
-        <v>8.076256020000001</v>
+        <v>7.990839640000001</v>
       </c>
       <c r="P23">
-        <v>32.30502408</v>
+        <v>31.96335856</v>
       </c>
       <c r="Q23">
-        <v>46.20502407999999</v>
+        <v>45.86335855999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08718895424447012</v>
+        <v>0.08763206707830633</v>
       </c>
       <c r="T23">
-        <v>0.8067477554447463</v>
+        <v>0.8153848493416977</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.502457491174409</v>
+        <v>5.252345787030118</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07808581232107893</v>
+        <v>0.07800195078902647</v>
       </c>
       <c r="C24">
-        <v>631.2589939439398</v>
+        <v>625.6065581630323</v>
       </c>
       <c r="D24">
-        <v>795.0749939439397</v>
+        <v>797.1455581630323</v>
       </c>
       <c r="E24">
-        <v>36.40599999999998</v>
+        <v>44.12899999999999</v>
       </c>
       <c r="F24">
-        <v>169.906</v>
+        <v>177.629</v>
       </c>
       <c r="G24">
         <v>6.09</v>
@@ -3377,28 +3377,28 @@
         <v>49.35</v>
       </c>
       <c r="M24">
-        <v>9.395801799999999</v>
+        <v>9.8228837</v>
       </c>
       <c r="N24">
-        <v>39.9541982</v>
+        <v>39.5271163</v>
       </c>
       <c r="O24">
-        <v>7.990839640000001</v>
+        <v>7.905423260000001</v>
       </c>
       <c r="P24">
-        <v>31.96335856</v>
+        <v>31.62169304</v>
       </c>
       <c r="Q24">
-        <v>45.86335855999999</v>
+        <v>45.52169304</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08763206707830633</v>
+        <v>0.08808668933639802</v>
       </c>
       <c r="T24">
-        <v>0.8153848493416977</v>
+        <v>0.8242462833398686</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.252345787030118</v>
+        <v>5.023982926724461</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07800195078902647</v>
+        <v>0.07791808925697401</v>
       </c>
       <c r="C25">
-        <v>625.6065581630323</v>
+        <v>619.9649350233278</v>
       </c>
       <c r="D25">
-        <v>797.1455581630323</v>
+        <v>799.2269350233278</v>
       </c>
       <c r="E25">
-        <v>44.12899999999999</v>
+        <v>51.852</v>
       </c>
       <c r="F25">
-        <v>177.629</v>
+        <v>185.352</v>
       </c>
       <c r="G25">
         <v>6.09</v>
@@ -3459,28 +3459,28 @@
         <v>49.35</v>
       </c>
       <c r="M25">
-        <v>9.8228837</v>
+        <v>10.2499656</v>
       </c>
       <c r="N25">
-        <v>39.5271163</v>
+        <v>39.1000344</v>
       </c>
       <c r="O25">
-        <v>7.905423260000001</v>
+        <v>7.82000688</v>
       </c>
       <c r="P25">
-        <v>31.62169304</v>
+        <v>31.28002752</v>
       </c>
       <c r="Q25">
-        <v>45.52169304</v>
+        <v>45.18002752</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08808668933639802</v>
+        <v>0.08855327533812368</v>
       </c>
       <c r="T25">
-        <v>0.8242462833398686</v>
+        <v>0.8333409129695704</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.023982926724461</v>
+        <v>4.814650304777608</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07791808925697401</v>
+        <v>0.07783422772492153</v>
       </c>
       <c r="C26">
-        <v>619.9649350233278</v>
+        <v>614.3342094431825</v>
       </c>
       <c r="D26">
-        <v>799.2269350233278</v>
+        <v>801.3192094431826</v>
       </c>
       <c r="E26">
-        <v>51.85199999999998</v>
+        <v>59.57499999999999</v>
       </c>
       <c r="F26">
-        <v>185.352</v>
+        <v>193.075</v>
       </c>
       <c r="G26">
         <v>6.09</v>
@@ -3541,28 +3541,28 @@
         <v>49.35</v>
       </c>
       <c r="M26">
-        <v>10.2499656</v>
+        <v>10.6770475</v>
       </c>
       <c r="N26">
-        <v>39.1000344</v>
+        <v>38.6729525</v>
       </c>
       <c r="O26">
-        <v>7.82000688</v>
+        <v>7.7345905</v>
       </c>
       <c r="P26">
-        <v>31.28002752</v>
+        <v>30.938362</v>
       </c>
       <c r="Q26">
-        <v>45.18002752</v>
+        <v>44.838362</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08855327533812368</v>
+        <v>0.08903230363322871</v>
       </c>
       <c r="T26">
-        <v>0.8333409129695702</v>
+        <v>0.8426780660560641</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.814650304777608</v>
+        <v>4.622064292586504</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07783422772492153</v>
+        <v>0.07827036619286906</v>
       </c>
       <c r="C27">
-        <v>614.3342094431825</v>
+        <v>595.8479759684635</v>
       </c>
       <c r="D27">
-        <v>801.3192094431826</v>
+        <v>790.5559759684635</v>
       </c>
       <c r="E27">
-        <v>59.57499999999999</v>
+        <v>67.298</v>
       </c>
       <c r="F27">
-        <v>193.075</v>
+        <v>200.798</v>
       </c>
       <c r="G27">
         <v>6.09</v>
@@ -3623,45 +3623,45 @@
         <v>49.35</v>
       </c>
       <c r="M27">
-        <v>10.6770475</v>
+        <v>11.6061244</v>
       </c>
       <c r="N27">
-        <v>38.6729525</v>
+        <v>37.7438756</v>
       </c>
       <c r="O27">
-        <v>7.7345905</v>
+        <v>7.548775120000001</v>
       </c>
       <c r="P27">
-        <v>30.938362</v>
+        <v>30.19510048</v>
       </c>
       <c r="Q27">
-        <v>44.838362</v>
+        <v>44.09510048</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08903230363322871</v>
+        <v>0.08952427863901224</v>
       </c>
       <c r="T27">
-        <v>0.8426780660560641</v>
+        <v>0.852267574631382</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.622064292586504</v>
+        <v>4.252065400918847</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07827036619286906</v>
+        <v>0.07820650466081661</v>
       </c>
       <c r="C28">
-        <v>595.8479759684635</v>
+        <v>589.682876653125</v>
       </c>
       <c r="D28">
-        <v>790.5559759684635</v>
+        <v>792.113876653125</v>
       </c>
       <c r="E28">
-        <v>67.298</v>
+        <v>75.02100000000002</v>
       </c>
       <c r="F28">
-        <v>200.798</v>
+        <v>208.521</v>
       </c>
       <c r="G28">
         <v>6.09</v>
@@ -3705,28 +3705,28 @@
         <v>49.35</v>
       </c>
       <c r="M28">
-        <v>11.6061244</v>
+        <v>12.0525138</v>
       </c>
       <c r="N28">
-        <v>37.7438756</v>
+        <v>37.2974862</v>
       </c>
       <c r="O28">
-        <v>7.548775120000001</v>
+        <v>7.459497240000001</v>
       </c>
       <c r="P28">
-        <v>30.19510048</v>
+        <v>29.83798896</v>
       </c>
       <c r="Q28">
-        <v>44.09510048</v>
+        <v>43.73798896</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08952427863901224</v>
+        <v>0.09002973241207754</v>
       </c>
       <c r="T28">
-        <v>0.852267574631382</v>
+        <v>0.8621198094690375</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.252065400918847</v>
+        <v>4.09458149718111</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07820650466081661</v>
+        <v>0.07892664312876413</v>
       </c>
       <c r="C29">
-        <v>589.682876653125</v>
+        <v>564.740151993561</v>
       </c>
       <c r="D29">
-        <v>792.113876653125</v>
+        <v>774.894151993561</v>
       </c>
       <c r="E29">
-        <v>75.02100000000002</v>
+        <v>82.744</v>
       </c>
       <c r="F29">
-        <v>208.521</v>
+        <v>216.244</v>
       </c>
       <c r="G29">
         <v>6.09</v>
@@ -3787,45 +3787,45 @@
         <v>49.35</v>
       </c>
       <c r="M29">
-        <v>12.0525138</v>
+        <v>13.2557572</v>
       </c>
       <c r="N29">
-        <v>37.2974862</v>
+        <v>36.0942428</v>
       </c>
       <c r="O29">
-        <v>7.459497240000001</v>
+        <v>7.218848560000001</v>
       </c>
       <c r="P29">
-        <v>29.83798896</v>
+        <v>28.87539424</v>
       </c>
       <c r="Q29">
-        <v>43.73798896</v>
+        <v>42.77539424</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09002973241207754</v>
+        <v>0.09054922656772796</v>
       </c>
       <c r="T29">
-        <v>0.8621198094690375</v>
+        <v>0.8722457174966278</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.09458149718111</v>
+        <v>3.722910676124937</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07892664312876413</v>
+        <v>0.07889078159671166</v>
       </c>
       <c r="C30">
-        <v>564.740151993561</v>
+        <v>557.8569294218388</v>
       </c>
       <c r="D30">
-        <v>774.894151993561</v>
+        <v>775.7339294218388</v>
       </c>
       <c r="E30">
-        <v>82.744</v>
+        <v>90.46700000000001</v>
       </c>
       <c r="F30">
-        <v>216.244</v>
+        <v>223.967</v>
       </c>
       <c r="G30">
         <v>6.09</v>
@@ -3869,28 +3869,28 @@
         <v>49.35</v>
       </c>
       <c r="M30">
-        <v>13.2557572</v>
+        <v>13.7291771</v>
       </c>
       <c r="N30">
-        <v>36.0942428</v>
+        <v>35.6208229</v>
       </c>
       <c r="O30">
-        <v>7.218848560000001</v>
+        <v>7.12416458</v>
       </c>
       <c r="P30">
-        <v>28.87539424</v>
+        <v>28.49665832</v>
       </c>
       <c r="Q30">
-        <v>42.77539424</v>
+        <v>42.39665832</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09054922656772796</v>
+        <v>0.09108335436156573</v>
       </c>
       <c r="T30">
-        <v>0.8722457174966278</v>
+        <v>0.8826568623700657</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.722910676124937</v>
+        <v>3.594534445913732</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07889078159671166</v>
+        <v>0.0795269200646592</v>
       </c>
       <c r="C31">
-        <v>557.8569294218388</v>
+        <v>535.502466114449</v>
       </c>
       <c r="D31">
-        <v>775.7339294218388</v>
+        <v>761.1024661144489</v>
       </c>
       <c r="E31">
-        <v>90.46699999999998</v>
+        <v>98.18999999999997</v>
       </c>
       <c r="F31">
-        <v>223.967</v>
+        <v>231.69</v>
       </c>
       <c r="G31">
         <v>6.09</v>
@@ -3951,45 +3951,45 @@
         <v>49.35</v>
       </c>
       <c r="M31">
-        <v>13.7291771</v>
+        <v>14.851329</v>
       </c>
       <c r="N31">
-        <v>35.6208229</v>
+        <v>34.498671</v>
       </c>
       <c r="O31">
-        <v>7.12416458</v>
+        <v>6.899734200000001</v>
       </c>
       <c r="P31">
-        <v>28.49665832</v>
+        <v>27.5989368</v>
       </c>
       <c r="Q31">
-        <v>42.39665832</v>
+        <v>41.4989368</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09108335436156573</v>
+        <v>0.09163274294951315</v>
       </c>
       <c r="T31">
-        <v>0.8826568623700657</v>
+        <v>0.8933654685256018</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.594534445913733</v>
+        <v>3.322934937337931</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0795269200646592</v>
+        <v>0.07951345853260673</v>
       </c>
       <c r="C32">
-        <v>535.502466114449</v>
+        <v>528.083368641474</v>
       </c>
       <c r="D32">
-        <v>761.1024661144489</v>
+        <v>761.4063686414739</v>
       </c>
       <c r="E32">
-        <v>98.18999999999997</v>
+        <v>105.913</v>
       </c>
       <c r="F32">
-        <v>231.69</v>
+        <v>239.413</v>
       </c>
       <c r="G32">
         <v>6.09</v>
@@ -4033,28 +4033,28 @@
         <v>49.35</v>
       </c>
       <c r="M32">
-        <v>14.851329</v>
+        <v>15.3463733</v>
       </c>
       <c r="N32">
-        <v>34.498671</v>
+        <v>34.0036267</v>
       </c>
       <c r="O32">
-        <v>6.899734200000001</v>
+        <v>6.80072534</v>
       </c>
       <c r="P32">
-        <v>27.5989368</v>
+        <v>27.20290136</v>
       </c>
       <c r="Q32">
-        <v>41.4989368</v>
+        <v>41.10290136</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09163274294951315</v>
+        <v>0.09219805584435758</v>
       </c>
       <c r="T32">
-        <v>0.8933654685256018</v>
+        <v>0.9043844690624578</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.322934937337931</v>
+        <v>3.215743487746385</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07951345853260673</v>
+        <v>0.07949999700055427</v>
       </c>
       <c r="C33">
-        <v>528.083368641474</v>
+        <v>520.6645139574587</v>
       </c>
       <c r="D33">
-        <v>761.4063686414739</v>
+        <v>761.7105139574586</v>
       </c>
       <c r="E33">
-        <v>105.913</v>
+        <v>113.636</v>
       </c>
       <c r="F33">
-        <v>239.413</v>
+        <v>247.136</v>
       </c>
       <c r="G33">
         <v>6.09</v>
@@ -4115,28 +4115,28 @@
         <v>49.35</v>
       </c>
       <c r="M33">
-        <v>15.3463733</v>
+        <v>15.8414176</v>
       </c>
       <c r="N33">
-        <v>34.0036267</v>
+        <v>33.5085824</v>
       </c>
       <c r="O33">
-        <v>6.80072534</v>
+        <v>6.701716480000001</v>
       </c>
       <c r="P33">
-        <v>27.20290136</v>
+        <v>26.80686592</v>
       </c>
       <c r="Q33">
-        <v>41.10290136</v>
+        <v>40.70686592</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09219805584435758</v>
+        <v>0.0927799955890504</v>
       </c>
       <c r="T33">
-        <v>0.9043844690624578</v>
+        <v>0.9157275578503978</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.215743487746385</v>
+        <v>3.11525150375431</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07949999700055427</v>
+        <v>0.07948653546850179</v>
       </c>
       <c r="C34">
-        <v>520.6645139574587</v>
+        <v>513.2459023534673</v>
       </c>
       <c r="D34">
-        <v>761.7105139574586</v>
+        <v>762.0149023534673</v>
       </c>
       <c r="E34">
-        <v>113.636</v>
+        <v>121.359</v>
       </c>
       <c r="F34">
-        <v>247.136</v>
+        <v>254.859</v>
       </c>
       <c r="G34">
         <v>6.09</v>
@@ -4197,28 +4197,28 @@
         <v>49.35</v>
       </c>
       <c r="M34">
-        <v>15.8414176</v>
+        <v>16.3364619</v>
       </c>
       <c r="N34">
-        <v>33.5085824</v>
+        <v>33.0135381</v>
       </c>
       <c r="O34">
-        <v>6.701716480000001</v>
+        <v>6.60270762</v>
       </c>
       <c r="P34">
-        <v>26.80686592</v>
+        <v>26.41083048</v>
       </c>
       <c r="Q34">
-        <v>40.70686592</v>
+        <v>40.31083047999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0927799955890504</v>
+        <v>0.09337930666940567</v>
       </c>
       <c r="T34">
-        <v>0.9157275578503978</v>
+        <v>0.9274092463036495</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.11525150375431</v>
+        <v>3.020849943034482</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07948653546850179</v>
+        <v>0.08159467393644933</v>
       </c>
       <c r="C35">
-        <v>513.2459023534673</v>
+        <v>460.6437973879429</v>
       </c>
       <c r="D35">
-        <v>762.0149023534673</v>
+        <v>717.1357973879428</v>
       </c>
       <c r="E35">
-        <v>121.359</v>
+        <v>129.082</v>
       </c>
       <c r="F35">
-        <v>254.859</v>
+        <v>262.582</v>
       </c>
       <c r="G35">
         <v>6.09</v>
@@ -4279,45 +4279,45 @@
         <v>49.35</v>
       </c>
       <c r="M35">
-        <v>16.3364619</v>
+        <v>18.8796458</v>
       </c>
       <c r="N35">
-        <v>33.0135381</v>
+        <v>30.4703542</v>
       </c>
       <c r="O35">
-        <v>6.60270762</v>
+        <v>6.094070840000001</v>
       </c>
       <c r="P35">
-        <v>26.41083048</v>
+        <v>24.37628336</v>
       </c>
       <c r="Q35">
-        <v>40.31083047999999</v>
+        <v>38.27628335999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09337930666940567</v>
+        <v>0.0939967786915899</v>
       </c>
       <c r="T35">
-        <v>0.9274092463036495</v>
+        <v>0.9394449253160906</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.020849943034482</v>
+        <v>2.613926157449415</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08159467393644933</v>
+        <v>0.08164361240439687</v>
       </c>
       <c r="C36">
-        <v>460.6437973879429</v>
+        <v>451.9416681964277</v>
       </c>
       <c r="D36">
-        <v>717.1357973879428</v>
+        <v>716.1566681964276</v>
       </c>
       <c r="E36">
-        <v>129.082</v>
+        <v>136.805</v>
       </c>
       <c r="F36">
-        <v>262.582</v>
+        <v>270.305</v>
       </c>
       <c r="G36">
         <v>6.09</v>
@@ -4361,28 +4361,28 @@
         <v>49.35</v>
       </c>
       <c r="M36">
-        <v>18.8796458</v>
+        <v>19.4349295</v>
       </c>
       <c r="N36">
-        <v>30.4703542</v>
+        <v>29.9150705</v>
       </c>
       <c r="O36">
-        <v>6.094070840000001</v>
+        <v>5.9830141</v>
       </c>
       <c r="P36">
-        <v>24.37628336</v>
+        <v>23.9320564</v>
       </c>
       <c r="Q36">
-        <v>38.27628335999999</v>
+        <v>37.8320564</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0939967786915899</v>
+        <v>0.09463324985291827</v>
       </c>
       <c r="T36">
-        <v>0.9394449253160906</v>
+        <v>0.95185093291353</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.613926157449415</v>
+        <v>2.539242552950861</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08164361240439687</v>
+        <v>0.0828157508723444</v>
       </c>
       <c r="C37">
-        <v>451.9416681964277</v>
+        <v>421.5408956242836</v>
       </c>
       <c r="D37">
-        <v>716.1566681964276</v>
+        <v>693.4788956242836</v>
       </c>
       <c r="E37">
-        <v>136.805</v>
+        <v>144.528</v>
       </c>
       <c r="F37">
-        <v>270.305</v>
+        <v>278.028</v>
       </c>
       <c r="G37">
         <v>6.09</v>
@@ -4443,45 +4443,45 @@
         <v>49.35</v>
       </c>
       <c r="M37">
-        <v>19.4349295</v>
+        <v>21.0745224</v>
       </c>
       <c r="N37">
-        <v>29.9150705</v>
+        <v>28.2754776</v>
       </c>
       <c r="O37">
-        <v>5.9830141</v>
+        <v>5.65509552</v>
       </c>
       <c r="P37">
-        <v>23.9320564</v>
+        <v>22.62038208</v>
       </c>
       <c r="Q37">
-        <v>37.8320564</v>
+        <v>36.52038208</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09463324985291827</v>
+        <v>0.09528961073803813</v>
       </c>
       <c r="T37">
-        <v>0.95185093291353</v>
+        <v>0.9646446282483893</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.539242552950861</v>
+        <v>2.341690077873366</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08281575087234441</v>
+        <v>0.08289588934029195</v>
       </c>
       <c r="C38">
-        <v>421.5408956242833</v>
+        <v>412.3197690868798</v>
       </c>
       <c r="D38">
-        <v>693.4788956242833</v>
+        <v>691.9807690868797</v>
       </c>
       <c r="E38">
-        <v>144.528</v>
+        <v>152.251</v>
       </c>
       <c r="F38">
-        <v>278.028</v>
+        <v>285.751</v>
       </c>
       <c r="G38">
         <v>6.09</v>
@@ -4525,28 +4525,28 @@
         <v>49.35</v>
       </c>
       <c r="M38">
-        <v>21.0745224</v>
+        <v>21.6599258</v>
       </c>
       <c r="N38">
-        <v>28.2754776</v>
+        <v>27.6900742</v>
       </c>
       <c r="O38">
-        <v>5.655095520000001</v>
+        <v>5.538014840000001</v>
       </c>
       <c r="P38">
-        <v>22.62038208</v>
+        <v>22.15205936</v>
       </c>
       <c r="Q38">
-        <v>36.52038208</v>
+        <v>36.05205936</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09528961073803813</v>
+        <v>0.09596680847665387</v>
       </c>
       <c r="T38">
-        <v>0.9646446282483891</v>
+        <v>0.977844472641498</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.341690077873366</v>
+        <v>2.278401156849762</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08289588934029195</v>
+        <v>0.08297602780823947</v>
       </c>
       <c r="C39">
-        <v>412.3197690868798</v>
+        <v>403.1051014194837</v>
       </c>
       <c r="D39">
-        <v>691.9807690868797</v>
+        <v>690.4891014194836</v>
       </c>
       <c r="E39">
-        <v>152.251</v>
+        <v>159.974</v>
       </c>
       <c r="F39">
-        <v>285.751</v>
+        <v>293.474</v>
       </c>
       <c r="G39">
         <v>6.09</v>
@@ -4607,28 +4607,28 @@
         <v>49.35</v>
       </c>
       <c r="M39">
-        <v>21.6599258</v>
+        <v>22.2453292</v>
       </c>
       <c r="N39">
-        <v>27.6900742</v>
+        <v>27.1046708</v>
       </c>
       <c r="O39">
-        <v>5.538014840000001</v>
+        <v>5.420934160000001</v>
       </c>
       <c r="P39">
-        <v>22.15205936</v>
+        <v>21.68373664</v>
       </c>
       <c r="Q39">
-        <v>36.05205936</v>
+        <v>35.58373664</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09596680847665387</v>
+        <v>0.09666585130361205</v>
       </c>
       <c r="T39">
-        <v>0.977844472641498</v>
+        <v>0.9914701184666425</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.278401156849762</v>
+        <v>2.218443231669505</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08297602780823947</v>
+        <v>0.083056166276187</v>
       </c>
       <c r="C40">
-        <v>403.1051014194837</v>
+        <v>393.8968509427699</v>
       </c>
       <c r="D40">
-        <v>690.4891014194836</v>
+        <v>689.0038509427699</v>
       </c>
       <c r="E40">
-        <v>159.974</v>
+        <v>167.697</v>
       </c>
       <c r="F40">
-        <v>293.474</v>
+        <v>301.197</v>
       </c>
       <c r="G40">
         <v>6.09</v>
@@ -4689,28 +4689,28 @@
         <v>49.35</v>
       </c>
       <c r="M40">
-        <v>22.2453292</v>
+        <v>22.8307326</v>
       </c>
       <c r="N40">
-        <v>27.1046708</v>
+        <v>26.5192674</v>
       </c>
       <c r="O40">
-        <v>5.420934160000001</v>
+        <v>5.303853480000001</v>
       </c>
       <c r="P40">
-        <v>21.68373664</v>
+        <v>21.21541392</v>
       </c>
       <c r="Q40">
-        <v>35.58373664</v>
+        <v>35.11541391999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09666585130361205</v>
+        <v>0.09738781356751969</v>
       </c>
       <c r="T40">
-        <v>0.9914701184666425</v>
+        <v>1.005542506777857</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.218443231669505</v>
+        <v>2.161560071883107</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.083056166276187</v>
+        <v>0.08313630474413454</v>
       </c>
       <c r="C41">
-        <v>393.8968509427699</v>
+        <v>384.6949763352559</v>
       </c>
       <c r="D41">
-        <v>689.0038509427699</v>
+        <v>687.5249763352559</v>
       </c>
       <c r="E41">
-        <v>167.697</v>
+        <v>175.42</v>
       </c>
       <c r="F41">
-        <v>301.197</v>
+        <v>308.92</v>
       </c>
       <c r="G41">
         <v>6.09</v>
@@ -4771,28 +4771,28 @@
         <v>49.35</v>
       </c>
       <c r="M41">
-        <v>22.8307326</v>
+        <v>23.416136</v>
       </c>
       <c r="N41">
-        <v>26.5192674</v>
+        <v>25.933864</v>
       </c>
       <c r="O41">
-        <v>5.303853480000001</v>
+        <v>5.1867728</v>
       </c>
       <c r="P41">
-        <v>21.21541392</v>
+        <v>20.7470912</v>
       </c>
       <c r="Q41">
-        <v>35.11541391999999</v>
+        <v>34.6470912</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09738781356751969</v>
+        <v>0.09813384124022423</v>
       </c>
       <c r="T41">
-        <v>1.005542506777857</v>
+        <v>1.020083974699446</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.161560071883107</v>
+        <v>2.10752107008603</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08313630474413454</v>
+        <v>0.08321644321208208</v>
       </c>
       <c r="C42">
-        <v>384.6949763352559</v>
+        <v>375.4994366294674</v>
       </c>
       <c r="D42">
-        <v>687.5249763352559</v>
+        <v>686.0524366294674</v>
       </c>
       <c r="E42">
-        <v>175.42</v>
+        <v>183.143</v>
       </c>
       <c r="F42">
-        <v>308.92</v>
+        <v>316.643</v>
       </c>
       <c r="G42">
         <v>6.09</v>
@@ -4853,28 +4853,28 @@
         <v>49.35</v>
       </c>
       <c r="M42">
-        <v>23.416136</v>
+        <v>24.00153940000001</v>
       </c>
       <c r="N42">
-        <v>25.933864</v>
+        <v>25.3484606</v>
       </c>
       <c r="O42">
-        <v>5.1867728</v>
+        <v>5.069692119999999</v>
       </c>
       <c r="P42">
-        <v>20.7470912</v>
+        <v>20.27876848</v>
       </c>
       <c r="Q42">
-        <v>34.6470912</v>
+        <v>34.17876848</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09813384124022423</v>
+        <v>0.09890515798657978</v>
       </c>
       <c r="T42">
-        <v>1.020083974699446</v>
+        <v>1.035118373737021</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.10752107008603</v>
+        <v>2.056118117157101</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08321644321208208</v>
+        <v>0.08329658168002961</v>
       </c>
       <c r="C43">
-        <v>375.4994366294674</v>
+        <v>366.3101912081564</v>
       </c>
       <c r="D43">
-        <v>686.0524366294674</v>
+        <v>684.5861912081564</v>
       </c>
       <c r="E43">
-        <v>183.143</v>
+        <v>190.866</v>
       </c>
       <c r="F43">
-        <v>316.643</v>
+        <v>324.366</v>
       </c>
       <c r="G43">
         <v>6.09</v>
@@ -4935,28 +4935,28 @@
         <v>49.35</v>
       </c>
       <c r="M43">
-        <v>24.00153940000001</v>
+        <v>24.5869428</v>
       </c>
       <c r="N43">
-        <v>25.3484606</v>
+        <v>24.7630572</v>
       </c>
       <c r="O43">
-        <v>5.069692119999999</v>
+        <v>4.952611440000001</v>
       </c>
       <c r="P43">
-        <v>20.27876848</v>
+        <v>19.81044576</v>
       </c>
       <c r="Q43">
-        <v>34.17876848</v>
+        <v>33.71044576</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09890515798657978</v>
+        <v>0.09970307186212002</v>
       </c>
       <c r="T43">
-        <v>1.035118373737021</v>
+        <v>1.050671200327616</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.056118117157101</v>
+        <v>2.007162923891457</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08329658168002961</v>
+        <v>0.08826152014797714</v>
       </c>
       <c r="C44">
-        <v>366.3101912081564</v>
+        <v>278.5399318658179</v>
       </c>
       <c r="D44">
-        <v>684.5861912081564</v>
+        <v>604.5389318658179</v>
       </c>
       <c r="E44">
-        <v>190.866</v>
+        <v>198.589</v>
       </c>
       <c r="F44">
-        <v>324.366</v>
+        <v>332.089</v>
       </c>
       <c r="G44">
         <v>6.09</v>
@@ -5017,45 +5017,45 @@
         <v>49.35</v>
       </c>
       <c r="M44">
-        <v>24.5869428</v>
+        <v>29.88801</v>
       </c>
       <c r="N44">
-        <v>24.7630572</v>
+        <v>19.46199</v>
       </c>
       <c r="O44">
-        <v>4.952611440000001</v>
+        <v>3.892398000000001</v>
       </c>
       <c r="P44">
-        <v>19.81044576</v>
+        <v>15.569592</v>
       </c>
       <c r="Q44">
-        <v>33.71044576</v>
+        <v>29.469592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09970307186212</v>
+        <v>0.1005289827157494</v>
       </c>
       <c r="T44">
-        <v>1.050671200327615</v>
+        <v>1.066769740131915</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.007162923891457</v>
+        <v>1.651163794444662</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08826152014797714</v>
+        <v>0.08845525861592468</v>
       </c>
       <c r="C45">
-        <v>278.5399318658179</v>
+        <v>268.0711403673085</v>
       </c>
       <c r="D45">
-        <v>604.5389318658179</v>
+        <v>601.7931403673084</v>
       </c>
       <c r="E45">
-        <v>198.589</v>
+        <v>206.312</v>
       </c>
       <c r="F45">
-        <v>332.089</v>
+        <v>339.812</v>
       </c>
       <c r="G45">
         <v>6.09</v>
@@ -5099,28 +5099,28 @@
         <v>49.35</v>
       </c>
       <c r="M45">
-        <v>29.88801</v>
+        <v>30.58308</v>
       </c>
       <c r="N45">
-        <v>19.46199</v>
+        <v>18.76692000000001</v>
       </c>
       <c r="O45">
-        <v>3.892398000000001</v>
+        <v>3.753384000000001</v>
       </c>
       <c r="P45">
-        <v>15.569592</v>
+        <v>15.01353600000001</v>
       </c>
       <c r="Q45">
-        <v>29.469592</v>
+        <v>28.913536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1005289827157494</v>
+        <v>0.1013843903855798</v>
       </c>
       <c r="T45">
-        <v>1.066769740131915</v>
+        <v>1.083443227786368</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.651163794444662</v>
+        <v>1.61363734457092</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08845525861592468</v>
+        <v>0.08864899708387221</v>
       </c>
       <c r="C46">
-        <v>268.0711403673085</v>
+        <v>257.6271786419295</v>
       </c>
       <c r="D46">
-        <v>601.7931403673084</v>
+        <v>599.0721786419294</v>
       </c>
       <c r="E46">
-        <v>206.312</v>
+        <v>214.035</v>
       </c>
       <c r="F46">
-        <v>339.812</v>
+        <v>347.535</v>
       </c>
       <c r="G46">
         <v>6.09</v>
@@ -5181,28 +5181,28 @@
         <v>49.35</v>
       </c>
       <c r="M46">
-        <v>30.58308</v>
+        <v>31.27815</v>
       </c>
       <c r="N46">
-        <v>18.76692000000001</v>
+        <v>18.07185</v>
       </c>
       <c r="O46">
-        <v>3.753384000000001</v>
+        <v>3.614370000000001</v>
       </c>
       <c r="P46">
-        <v>15.01353600000001</v>
+        <v>14.45748</v>
       </c>
       <c r="Q46">
-        <v>28.913536</v>
+        <v>28.35748</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1013843903855798</v>
+        <v>0.1022709037888586</v>
       </c>
       <c r="T46">
-        <v>1.083443227786368</v>
+        <v>1.100723024082801</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.61363734457092</v>
+        <v>1.577778736913788</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08864899708387221</v>
+        <v>0.08884273555181975</v>
       </c>
       <c r="C47">
-        <v>257.6271786419295</v>
+        <v>247.2077114078627</v>
       </c>
       <c r="D47">
-        <v>599.0721786419294</v>
+        <v>596.3757114078627</v>
       </c>
       <c r="E47">
-        <v>214.035</v>
+        <v>221.758</v>
       </c>
       <c r="F47">
-        <v>347.535</v>
+        <v>355.258</v>
       </c>
       <c r="G47">
         <v>6.09</v>
@@ -5263,28 +5263,28 @@
         <v>49.35</v>
       </c>
       <c r="M47">
-        <v>31.27815</v>
+        <v>31.97322</v>
       </c>
       <c r="N47">
-        <v>18.07185</v>
+        <v>17.37678</v>
       </c>
       <c r="O47">
-        <v>3.614370000000001</v>
+        <v>3.475356000000001</v>
       </c>
       <c r="P47">
-        <v>14.45748</v>
+        <v>13.901424</v>
       </c>
       <c r="Q47">
-        <v>28.35748</v>
+        <v>27.801424</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1022709037888586</v>
+        <v>0.1031902510218884</v>
       </c>
       <c r="T47">
-        <v>1.100723024082801</v>
+        <v>1.118642812834658</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.577778736913788</v>
+        <v>1.543479199154793</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08884273555181975</v>
+        <v>0.08903647401976728</v>
       </c>
       <c r="C48">
-        <v>247.2077114078627</v>
+        <v>236.8124093927527</v>
       </c>
       <c r="D48">
-        <v>596.3757114078627</v>
+        <v>593.7034093927526</v>
       </c>
       <c r="E48">
-        <v>221.758</v>
+        <v>229.481</v>
       </c>
       <c r="F48">
-        <v>355.258</v>
+        <v>362.981</v>
       </c>
       <c r="G48">
         <v>6.09</v>
@@ -5345,28 +5345,28 @@
         <v>49.35</v>
       </c>
       <c r="M48">
-        <v>31.97322</v>
+        <v>32.66829</v>
       </c>
       <c r="N48">
-        <v>17.37678</v>
+        <v>16.68171</v>
       </c>
       <c r="O48">
-        <v>3.475356000000001</v>
+        <v>3.336342000000001</v>
       </c>
       <c r="P48">
-        <v>13.901424</v>
+        <v>13.345368</v>
       </c>
       <c r="Q48">
-        <v>27.801424</v>
+        <v>27.245368</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1031902510218884</v>
+        <v>0.1041442906033345</v>
       </c>
       <c r="T48">
-        <v>1.118642812834658</v>
+        <v>1.137238820029981</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.543479199154793</v>
+        <v>1.510639216194053</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08903647401976728</v>
+        <v>0.1126594268200569</v>
       </c>
       <c r="C49">
-        <v>236.8124093927527</v>
+        <v>19.32052137637049</v>
       </c>
       <c r="D49">
-        <v>593.7034093927526</v>
+        <v>383.9345213763705</v>
       </c>
       <c r="E49">
-        <v>229.481</v>
+        <v>237.204</v>
       </c>
       <c r="F49">
-        <v>362.981</v>
+        <v>370.704</v>
       </c>
       <c r="G49">
         <v>6.09</v>
@@ -5427,45 +5427,45 @@
         <v>49.35</v>
       </c>
       <c r="M49">
-        <v>32.66829</v>
+        <v>54.4193472</v>
       </c>
       <c r="N49">
-        <v>16.68171</v>
+        <v>-5.069347200000003</v>
       </c>
       <c r="O49">
-        <v>3.336342000000001</v>
+        <v>-1.013869440000001</v>
       </c>
       <c r="P49">
-        <v>13.345368</v>
+        <v>-4.055477760000002</v>
       </c>
       <c r="Q49">
-        <v>27.245368</v>
+        <v>9.844522239999996</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1041442906033345</v>
+        <v>0.1057219895943433</v>
       </c>
       <c r="T49">
-        <v>1.137238820029981</v>
+        <v>1.167991109934332</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2</v>
+        <v>0.1813693200641701</v>
       </c>
       <c r="W49">
-        <v>0.07199999999999999</v>
+        <v>0.1201749838145798</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.510639216194053</v>
+        <v>0.9068466003208505</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1126594268200569</v>
+        <v>0.1136694268200569</v>
       </c>
       <c r="C50">
-        <v>19.32052137637055</v>
+        <v>5.883993433689682</v>
       </c>
       <c r="D50">
-        <v>383.9345213763705</v>
+        <v>378.2209934336897</v>
       </c>
       <c r="E50">
-        <v>237.204</v>
+        <v>244.927</v>
       </c>
       <c r="F50">
-        <v>370.704</v>
+        <v>378.427</v>
       </c>
       <c r="G50">
         <v>6.09</v>
@@ -5509,37 +5509,37 @@
         <v>49.35</v>
       </c>
       <c r="M50">
-        <v>54.4193472</v>
+        <v>55.5530836</v>
       </c>
       <c r="N50">
-        <v>-5.069347199999996</v>
+        <v>-6.203083599999999</v>
       </c>
       <c r="O50">
-        <v>-1.013869439999999</v>
+        <v>-1.24061672</v>
       </c>
       <c r="P50">
-        <v>-4.055477759999997</v>
+        <v>-4.962466879999999</v>
       </c>
       <c r="Q50">
-        <v>9.844522240000002</v>
+        <v>8.937533119999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1057219895943433</v>
+        <v>0.1068969305667815</v>
       </c>
       <c r="T50">
-        <v>1.167991109934332</v>
+        <v>1.190892896403632</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1813693200641701</v>
+        <v>0.177667905368983</v>
       </c>
       <c r="W50">
-        <v>0.1201749838145798</v>
+        <v>0.1207183514918333</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9068466003208506</v>
+        <v>0.8883395268449149</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1136694268200569</v>
+        <v>0.1146794268200569</v>
       </c>
       <c r="C51">
-        <v>5.883993433689682</v>
+        <v>-7.384976110540038</v>
       </c>
       <c r="D51">
-        <v>378.2209934336897</v>
+        <v>372.67502388946</v>
       </c>
       <c r="E51">
-        <v>244.927</v>
+        <v>252.65</v>
       </c>
       <c r="F51">
-        <v>378.427</v>
+        <v>386.15</v>
       </c>
       <c r="G51">
         <v>6.09</v>
@@ -5591,37 +5591,37 @@
         <v>49.35</v>
       </c>
       <c r="M51">
-        <v>55.5530836</v>
+        <v>56.68682</v>
       </c>
       <c r="N51">
-        <v>-6.203083599999999</v>
+        <v>-7.336820000000003</v>
       </c>
       <c r="O51">
-        <v>-1.24061672</v>
+        <v>-1.467364000000001</v>
       </c>
       <c r="P51">
-        <v>-4.962466879999999</v>
+        <v>-5.869456000000002</v>
       </c>
       <c r="Q51">
-        <v>8.937533119999999</v>
+        <v>8.030543999999995</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1068969305667815</v>
+        <v>0.1081188691781171</v>
       </c>
       <c r="T51">
-        <v>1.190892896403632</v>
+        <v>1.214710754331705</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.177667905368983</v>
+        <v>0.1741145472616033</v>
       </c>
       <c r="W51">
-        <v>0.1207183514918333</v>
+        <v>0.1212399844619966</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8883395268449149</v>
+        <v>0.8705727363080166</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1146794268200569</v>
+        <v>0.1156894268200569</v>
       </c>
       <c r="C52">
-        <v>-7.384976110540038</v>
+        <v>-20.49365161618522</v>
       </c>
       <c r="D52">
-        <v>372.67502388946</v>
+        <v>367.2893483838148</v>
       </c>
       <c r="E52">
-        <v>252.65</v>
+        <v>260.373</v>
       </c>
       <c r="F52">
-        <v>386.15</v>
+        <v>393.873</v>
       </c>
       <c r="G52">
         <v>6.09</v>
@@ -5673,37 +5673,37 @@
         <v>49.35</v>
       </c>
       <c r="M52">
-        <v>56.68682</v>
+        <v>57.8205564</v>
       </c>
       <c r="N52">
-        <v>-7.336820000000003</v>
+        <v>-8.4705564</v>
       </c>
       <c r="O52">
-        <v>-1.467364000000001</v>
+        <v>-1.69411128</v>
       </c>
       <c r="P52">
-        <v>-5.869456000000002</v>
+        <v>-6.77644512</v>
       </c>
       <c r="Q52">
-        <v>8.030543999999995</v>
+        <v>7.123554879999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1081188691781171</v>
+        <v>0.1093906828348133</v>
       </c>
       <c r="T52">
-        <v>1.214710754331705</v>
+        <v>1.23950076972623</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1741145472616033</v>
+        <v>0.1707005365309837</v>
       </c>
       <c r="W52">
-        <v>0.1212399844619966</v>
+        <v>0.1217411612372516</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8705727363080166</v>
+        <v>0.8535026826549182</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1156894268200569</v>
+        <v>0.1166994268200569</v>
       </c>
       <c r="C53">
-        <v>-20.49365161618522</v>
+        <v>-33.44888350445058</v>
       </c>
       <c r="D53">
-        <v>367.2893483838148</v>
+        <v>362.0571164955495</v>
       </c>
       <c r="E53">
-        <v>260.373</v>
+        <v>268.096</v>
       </c>
       <c r="F53">
-        <v>393.873</v>
+        <v>401.596</v>
       </c>
       <c r="G53">
         <v>6.09</v>
@@ -5755,37 +5755,37 @@
         <v>49.35</v>
       </c>
       <c r="M53">
-        <v>57.8205564</v>
+        <v>58.9542928</v>
       </c>
       <c r="N53">
-        <v>-8.4705564</v>
+        <v>-9.604292800000003</v>
       </c>
       <c r="O53">
-        <v>-1.69411128</v>
+        <v>-1.920858560000001</v>
       </c>
       <c r="P53">
-        <v>-6.77644512</v>
+        <v>-7.683434240000002</v>
       </c>
       <c r="Q53">
-        <v>7.123554879999999</v>
+        <v>6.216565759999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1093906828348133</v>
+        <v>0.1107154887272053</v>
       </c>
       <c r="T53">
-        <v>1.23950076972623</v>
+        <v>1.265323702428859</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1707005365309837</v>
+        <v>0.1674178339053878</v>
       </c>
       <c r="W53">
-        <v>0.1217411612372516</v>
+        <v>0.1222230619826891</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8535026826549182</v>
+        <v>0.8370891695269389</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1166994268200569</v>
+        <v>0.1177094268200569</v>
       </c>
       <c r="C54">
-        <v>-33.44888350445058</v>
+        <v>-46.25713732764643</v>
       </c>
       <c r="D54">
-        <v>362.0571164955495</v>
+        <v>356.9718626723536</v>
       </c>
       <c r="E54">
-        <v>268.096</v>
+        <v>275.819</v>
       </c>
       <c r="F54">
-        <v>401.596</v>
+        <v>409.319</v>
       </c>
       <c r="G54">
         <v>6.09</v>
@@ -5837,37 +5837,37 @@
         <v>49.35</v>
       </c>
       <c r="M54">
-        <v>58.9542928</v>
+        <v>60.08802920000001</v>
       </c>
       <c r="N54">
-        <v>-9.604292800000003</v>
+        <v>-10.73802920000001</v>
       </c>
       <c r="O54">
-        <v>-1.920858560000001</v>
+        <v>-2.147605840000002</v>
       </c>
       <c r="P54">
-        <v>-7.683434240000002</v>
+        <v>-8.590423360000006</v>
       </c>
       <c r="Q54">
-        <v>6.216565759999996</v>
+        <v>5.309576639999992</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1107154887272053</v>
+        <v>0.1120966693384224</v>
       </c>
       <c r="T54">
-        <v>1.265323702428859</v>
+        <v>1.292245483331601</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1674178339053878</v>
+        <v>0.1642590068505692</v>
       </c>
       <c r="W54">
-        <v>0.1222230619826891</v>
+        <v>0.1226867777943365</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8370891695269389</v>
+        <v>0.8212950342528458</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1177094268200569</v>
+        <v>0.1187194268200569</v>
       </c>
       <c r="C55">
-        <v>-46.25713732764643</v>
+        <v>-58.9245204230977</v>
       </c>
       <c r="D55">
-        <v>356.9718626723536</v>
+        <v>352.0274795769024</v>
       </c>
       <c r="E55">
-        <v>275.819</v>
+        <v>283.542</v>
       </c>
       <c r="F55">
-        <v>409.319</v>
+        <v>417.042</v>
       </c>
       <c r="G55">
         <v>6.09</v>
@@ -5919,37 +5919,37 @@
         <v>49.35</v>
       </c>
       <c r="M55">
-        <v>60.08802920000001</v>
+        <v>61.22176560000001</v>
       </c>
       <c r="N55">
-        <v>-10.73802920000001</v>
+        <v>-11.87176560000001</v>
       </c>
       <c r="O55">
-        <v>-2.147605840000002</v>
+        <v>-2.374353120000002</v>
       </c>
       <c r="P55">
-        <v>-8.590423360000006</v>
+        <v>-9.497412480000008</v>
       </c>
       <c r="Q55">
-        <v>5.309576639999992</v>
+        <v>4.40258751999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1120966693384224</v>
+        <v>0.113537901280562</v>
       </c>
       <c r="T55">
-        <v>1.292245483331601</v>
+        <v>1.320337776447506</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1642590068505692</v>
+        <v>0.1612171733903734</v>
       </c>
       <c r="W55">
-        <v>0.1226867777943365</v>
+        <v>0.1231333189462932</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8212950342528458</v>
+        <v>0.8060858669518671</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1187194268200569</v>
+        <v>0.1502284900551536</v>
       </c>
       <c r="C56">
-        <v>-58.9245204230977</v>
+        <v>-172.8642828087465</v>
       </c>
       <c r="D56">
-        <v>352.0274795769024</v>
+        <v>245.8107171912535</v>
       </c>
       <c r="E56">
-        <v>283.542</v>
+        <v>291.265</v>
       </c>
       <c r="F56">
-        <v>417.042</v>
+        <v>424.765</v>
       </c>
       <c r="G56">
         <v>6.09</v>
@@ -6001,45 +6001,45 @@
         <v>49.35</v>
       </c>
       <c r="M56">
-        <v>61.22176560000001</v>
+        <v>85.292812</v>
       </c>
       <c r="N56">
-        <v>-11.87176560000001</v>
+        <v>-35.942812</v>
       </c>
       <c r="O56">
-        <v>-2.374353120000002</v>
+        <v>-7.188562399999999</v>
       </c>
       <c r="P56">
-        <v>-9.497412480000008</v>
+        <v>-28.7542496</v>
       </c>
       <c r="Q56">
-        <v>4.40258751999999</v>
+        <v>-14.8542496</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.113537901280562</v>
+        <v>0.1168188840536785</v>
       </c>
       <c r="T56">
-        <v>1.320337776447506</v>
+        <v>1.384290237585569</v>
       </c>
       <c r="U56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1612171733903734</v>
+        <v>0.1157190127580739</v>
       </c>
       <c r="W56">
-        <v>0.1231333189462932</v>
+        <v>0.1775636222381788</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8060858669518671</v>
+        <v>0.5785950637903696</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1502284900551536</v>
+        <v>0.1517784900551536</v>
       </c>
       <c r="C57">
-        <v>-172.8642828087465</v>
+        <v>-184.1824143439114</v>
       </c>
       <c r="D57">
-        <v>245.8107171912535</v>
+        <v>242.2155856560886</v>
       </c>
       <c r="E57">
-        <v>291.265</v>
+        <v>298.988</v>
       </c>
       <c r="F57">
-        <v>424.765</v>
+        <v>432.488</v>
       </c>
       <c r="G57">
         <v>6.09</v>
@@ -6083,37 +6083,37 @@
         <v>49.35</v>
       </c>
       <c r="M57">
-        <v>85.292812</v>
+        <v>86.8435904</v>
       </c>
       <c r="N57">
-        <v>-35.942812</v>
+        <v>-37.4935904</v>
       </c>
       <c r="O57">
-        <v>-7.188562399999999</v>
+        <v>-7.49871808</v>
       </c>
       <c r="P57">
-        <v>-28.7542496</v>
+        <v>-29.99487232</v>
       </c>
       <c r="Q57">
-        <v>-14.8542496</v>
+        <v>-16.09487232</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1168188840536785</v>
+        <v>0.118432949600353</v>
       </c>
       <c r="T57">
-        <v>1.384290237585569</v>
+        <v>1.415751379348877</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1157190127580739</v>
+        <v>0.1136526018159655</v>
       </c>
       <c r="W57">
-        <v>0.1775636222381788</v>
+        <v>0.1779785575553541</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5785950637903696</v>
+        <v>0.5682630090798273</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1517784900551536</v>
+        <v>0.1533284900551536</v>
       </c>
       <c r="C58">
-        <v>-184.1824143439114</v>
+        <v>-195.3968997872052</v>
       </c>
       <c r="D58">
-        <v>242.2155856560886</v>
+        <v>238.7241002127948</v>
       </c>
       <c r="E58">
-        <v>298.988</v>
+        <v>306.711</v>
       </c>
       <c r="F58">
-        <v>432.488</v>
+        <v>440.211</v>
       </c>
       <c r="G58">
         <v>6.09</v>
@@ -6165,37 +6165,37 @@
         <v>49.35</v>
       </c>
       <c r="M58">
-        <v>86.8435904</v>
+        <v>88.39436880000001</v>
       </c>
       <c r="N58">
-        <v>-37.4935904</v>
+        <v>-39.04436880000001</v>
       </c>
       <c r="O58">
-        <v>-7.49871808</v>
+        <v>-7.808873760000002</v>
       </c>
       <c r="P58">
-        <v>-29.99487232</v>
+        <v>-31.23549504000001</v>
       </c>
       <c r="Q58">
-        <v>-16.09487232</v>
+        <v>-17.33549504000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.118432949600353</v>
+        <v>0.1201220879631519</v>
       </c>
       <c r="T58">
-        <v>1.415751379348877</v>
+        <v>1.448675830031409</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1136526018159655</v>
+        <v>0.1116586965209485</v>
       </c>
       <c r="W58">
-        <v>0.1779785575553541</v>
+        <v>0.1783789337385935</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5682630090798273</v>
+        <v>0.5582934826047425</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1533284900551536</v>
+        <v>0.1548784900551536</v>
       </c>
       <c r="C59">
-        <v>-195.3968997872052</v>
+        <v>-206.5121575562919</v>
       </c>
       <c r="D59">
-        <v>238.7241002127948</v>
+        <v>235.3318424437082</v>
       </c>
       <c r="E59">
-        <v>306.711</v>
+        <v>314.434</v>
       </c>
       <c r="F59">
-        <v>440.211</v>
+        <v>447.934</v>
       </c>
       <c r="G59">
         <v>6.09</v>
@@ -6247,37 +6247,37 @@
         <v>49.35</v>
       </c>
       <c r="M59">
-        <v>88.39436880000001</v>
+        <v>89.94514720000001</v>
       </c>
       <c r="N59">
-        <v>-39.04436880000001</v>
+        <v>-40.59514720000001</v>
       </c>
       <c r="O59">
-        <v>-7.808873760000002</v>
+        <v>-8.119029440000002</v>
       </c>
       <c r="P59">
-        <v>-31.23549504000001</v>
+        <v>-32.47611776000001</v>
       </c>
       <c r="Q59">
-        <v>-17.33549504000001</v>
+        <v>-18.57611776000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1201220879631519</v>
+        <v>0.1218916614860841</v>
       </c>
       <c r="T59">
-        <v>1.448675830031409</v>
+        <v>1.483168111698824</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1116586965209485</v>
+        <v>0.1097335465809322</v>
       </c>
       <c r="W59">
-        <v>0.1783789337385935</v>
+        <v>0.1787655038465488</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5582934826047425</v>
+        <v>0.5486677329046608</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1548784900551536</v>
+        <v>0.1564284900551536</v>
       </c>
       <c r="C60">
-        <v>-206.5121575562918</v>
+        <v>-217.5323584455555</v>
       </c>
       <c r="D60">
-        <v>235.3318424437082</v>
+        <v>232.0346415544444</v>
       </c>
       <c r="E60">
-        <v>314.434</v>
+        <v>322.1569999999999</v>
       </c>
       <c r="F60">
-        <v>447.934</v>
+        <v>455.6569999999999</v>
       </c>
       <c r="G60">
         <v>6.09</v>
@@ -6329,37 +6329,37 @@
         <v>49.35</v>
       </c>
       <c r="M60">
-        <v>89.94514719999999</v>
+        <v>91.49592559999999</v>
       </c>
       <c r="N60">
-        <v>-40.59514719999999</v>
+        <v>-42.14592559999999</v>
       </c>
       <c r="O60">
-        <v>-8.119029439999998</v>
+        <v>-8.429185119999998</v>
       </c>
       <c r="P60">
-        <v>-32.47611775999999</v>
+        <v>-33.71674047999999</v>
       </c>
       <c r="Q60">
-        <v>-18.57611776</v>
+        <v>-19.81674047999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1218916614860841</v>
+        <v>0.1237475556686715</v>
       </c>
       <c r="T60">
-        <v>1.483168111698824</v>
+        <v>1.519342943691478</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1097335465809322</v>
+        <v>0.1078736559609164</v>
       </c>
       <c r="W60">
-        <v>0.1787655038465488</v>
+        <v>0.179138969883048</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5486677329046609</v>
+        <v>0.5393682798045818</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1564284900551536</v>
+        <v>0.1579784900551536</v>
       </c>
       <c r="C61">
-        <v>-217.5323584455555</v>
+        <v>-228.4614427334841</v>
       </c>
       <c r="D61">
-        <v>232.0346415544444</v>
+        <v>228.8285572665158</v>
       </c>
       <c r="E61">
-        <v>322.1569999999999</v>
+        <v>329.8799999999999</v>
       </c>
       <c r="F61">
-        <v>455.6569999999999</v>
+        <v>463.3799999999999</v>
       </c>
       <c r="G61">
         <v>6.09</v>
@@ -6411,37 +6411,37 @@
         <v>49.35</v>
       </c>
       <c r="M61">
-        <v>91.49592559999999</v>
+        <v>93.04670399999999</v>
       </c>
       <c r="N61">
-        <v>-42.14592559999999</v>
+        <v>-43.69670399999999</v>
       </c>
       <c r="O61">
-        <v>-8.429185119999998</v>
+        <v>-8.739340799999999</v>
       </c>
       <c r="P61">
-        <v>-33.71674047999999</v>
+        <v>-34.95736319999999</v>
       </c>
       <c r="Q61">
-        <v>-19.81674047999999</v>
+        <v>-21.05736319999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1237475556686715</v>
+        <v>0.1256962445603883</v>
       </c>
       <c r="T61">
-        <v>1.519342943691478</v>
+        <v>1.557326517283765</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1078736559609164</v>
+        <v>0.1060757616949011</v>
       </c>
       <c r="W61">
-        <v>0.179138969883048</v>
+        <v>0.1794999870516639</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5393682798045818</v>
+        <v>0.5303788084745056</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1579784900551536</v>
+        <v>0.1595284900551536</v>
       </c>
       <c r="C62">
-        <v>-228.4614427334841</v>
+        <v>-239.3031358911185</v>
       </c>
       <c r="D62">
-        <v>228.8285572665158</v>
+        <v>225.7098641088814</v>
       </c>
       <c r="E62">
-        <v>329.8799999999999</v>
+        <v>337.603</v>
       </c>
       <c r="F62">
-        <v>463.3799999999999</v>
+        <v>471.103</v>
       </c>
       <c r="G62">
         <v>6.09</v>
@@ -6493,37 +6493,37 @@
         <v>49.35</v>
       </c>
       <c r="M62">
-        <v>93.04670399999999</v>
+        <v>94.59748239999999</v>
       </c>
       <c r="N62">
-        <v>-43.69670399999999</v>
+        <v>-45.24748239999999</v>
       </c>
       <c r="O62">
-        <v>-8.739340799999999</v>
+        <v>-9.049496479999998</v>
       </c>
       <c r="P62">
-        <v>-34.95736319999999</v>
+        <v>-36.19798591999999</v>
       </c>
       <c r="Q62">
-        <v>-21.05736319999999</v>
+        <v>-22.29798592</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1256962445603883</v>
+        <v>0.1277448662157828</v>
       </c>
       <c r="T62">
-        <v>1.557326517283765</v>
+        <v>1.597257966444887</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1060757616949011</v>
+        <v>0.1043368147818699</v>
       </c>
       <c r="W62">
-        <v>0.1794999870516639</v>
+        <v>0.1798491675918005</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5303788084745056</v>
+        <v>0.5216840739093497</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1595284900551536</v>
+        <v>0.1610784900551536</v>
       </c>
       <c r="C63">
-        <v>-239.3031358911185</v>
+        <v>-250.0609630232347</v>
       </c>
       <c r="D63">
-        <v>225.7098641088814</v>
+        <v>222.6750369767653</v>
       </c>
       <c r="E63">
-        <v>337.603</v>
+        <v>345.326</v>
       </c>
       <c r="F63">
-        <v>471.103</v>
+        <v>478.826</v>
       </c>
       <c r="G63">
         <v>6.09</v>
@@ -6575,37 +6575,37 @@
         <v>49.35</v>
       </c>
       <c r="M63">
-        <v>94.59748239999999</v>
+        <v>96.1482608</v>
       </c>
       <c r="N63">
-        <v>-45.24748239999999</v>
+        <v>-46.7982608</v>
       </c>
       <c r="O63">
-        <v>-9.049496479999998</v>
+        <v>-9.359652160000001</v>
       </c>
       <c r="P63">
-        <v>-36.19798591999999</v>
+        <v>-37.43860864</v>
       </c>
       <c r="Q63">
-        <v>-22.29798592</v>
+        <v>-23.53860864</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1277448662157828</v>
+        <v>0.1299013100635666</v>
       </c>
       <c r="T63">
-        <v>1.597257966444887</v>
+        <v>1.639291070825016</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1043368147818699</v>
+        <v>0.1026539629305495</v>
       </c>
       <c r="W63">
-        <v>0.1798491675918005</v>
+        <v>0.1801870842435457</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5216840739093497</v>
+        <v>0.5132698146527472</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1610784900551536</v>
+        <v>0.1626284900551536</v>
       </c>
       <c r="C64">
-        <v>-250.0609630232347</v>
+        <v>-260.7382621599526</v>
       </c>
       <c r="D64">
-        <v>222.6750369767653</v>
+        <v>219.7207378400474</v>
       </c>
       <c r="E64">
-        <v>345.326</v>
+        <v>353.049</v>
       </c>
       <c r="F64">
-        <v>478.826</v>
+        <v>486.549</v>
       </c>
       <c r="G64">
         <v>6.09</v>
@@ -6657,37 +6657,37 @@
         <v>49.35</v>
       </c>
       <c r="M64">
-        <v>96.1482608</v>
+        <v>97.6990392</v>
       </c>
       <c r="N64">
-        <v>-46.7982608</v>
+        <v>-48.3490392</v>
       </c>
       <c r="O64">
-        <v>-9.359652160000001</v>
+        <v>-9.669807840000001</v>
       </c>
       <c r="P64">
-        <v>-37.43860864</v>
+        <v>-38.67923136</v>
       </c>
       <c r="Q64">
-        <v>-23.53860864</v>
+        <v>-24.77923136</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1299013100635666</v>
+        <v>0.132174318443663</v>
       </c>
       <c r="T64">
-        <v>1.639291070825016</v>
+        <v>1.683596234901367</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1026539629305495</v>
+        <v>0.1010245349475249</v>
       </c>
       <c r="W64">
-        <v>0.1801870842435457</v>
+        <v>0.180514273382537</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5132698146527472</v>
+        <v>0.5051226747376243</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1626284900551536</v>
+        <v>0.1869009217221287</v>
       </c>
       <c r="C65">
-        <v>-260.7382621599526</v>
+        <v>-306.2580145124463</v>
       </c>
       <c r="D65">
-        <v>219.7207378400474</v>
+        <v>181.9239854875537</v>
       </c>
       <c r="E65">
-        <v>353.049</v>
+        <v>360.772</v>
       </c>
       <c r="F65">
-        <v>486.549</v>
+        <v>494.272</v>
       </c>
       <c r="G65">
         <v>6.09</v>
@@ -6739,45 +6739,45 @@
         <v>49.35</v>
       </c>
       <c r="M65">
-        <v>97.6990392</v>
+        <v>116.5493376</v>
       </c>
       <c r="N65">
-        <v>-48.3490392</v>
+        <v>-67.19933760000001</v>
       </c>
       <c r="O65">
-        <v>-9.669807840000001</v>
+        <v>-13.43986752</v>
       </c>
       <c r="P65">
-        <v>-38.67923136</v>
+        <v>-53.75947008000001</v>
       </c>
       <c r="Q65">
-        <v>-24.77923136</v>
+        <v>-39.85947008000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.132174318443663</v>
+        <v>0.1354692485864733</v>
       </c>
       <c r="T65">
-        <v>1.683596234901367</v>
+        <v>1.747820556234991</v>
       </c>
       <c r="U65">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1010245349475249</v>
+        <v>0.08468516598416087</v>
       </c>
       <c r="W65">
-        <v>0.180514273382537</v>
+        <v>0.2158312378609349</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5051226747376243</v>
+        <v>0.4234258299208042</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1869009217221287</v>
+        <v>0.1888009217221287</v>
       </c>
       <c r="C66">
-        <v>-306.2580145124463</v>
+        <v>-316.3981707675508</v>
       </c>
       <c r="D66">
-        <v>181.9239854875537</v>
+        <v>179.5068292324492</v>
       </c>
       <c r="E66">
-        <v>360.772</v>
+        <v>368.495</v>
       </c>
       <c r="F66">
-        <v>494.272</v>
+        <v>501.995</v>
       </c>
       <c r="G66">
         <v>6.09</v>
@@ -6821,37 +6821,37 @@
         <v>49.35</v>
       </c>
       <c r="M66">
-        <v>116.5493376</v>
+        <v>118.370421</v>
       </c>
       <c r="N66">
-        <v>-67.19933760000001</v>
+        <v>-69.020421</v>
       </c>
       <c r="O66">
-        <v>-13.43986752</v>
+        <v>-13.8040842</v>
       </c>
       <c r="P66">
-        <v>-53.75947008000001</v>
+        <v>-55.2163368</v>
       </c>
       <c r="Q66">
-        <v>-39.85947008000001</v>
+        <v>-41.3163368</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1354692485864733</v>
+        <v>0.1380312271175154</v>
       </c>
       <c r="T66">
-        <v>1.747820556234991</v>
+        <v>1.797758286413133</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08468516598416087</v>
+        <v>0.08338231727671223</v>
       </c>
       <c r="W66">
-        <v>0.2158312378609349</v>
+        <v>0.2161384495861513</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4234258299208042</v>
+        <v>0.4169115863835612</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1888009217221287</v>
+        <v>0.1907009217221287</v>
       </c>
       <c r="C67">
-        <v>-316.3981707675508</v>
+        <v>-326.4749375447953</v>
       </c>
       <c r="D67">
-        <v>179.5068292324492</v>
+        <v>177.1530624552047</v>
       </c>
       <c r="E67">
-        <v>368.495</v>
+        <v>376.218</v>
       </c>
       <c r="F67">
-        <v>501.995</v>
+        <v>509.718</v>
       </c>
       <c r="G67">
         <v>6.09</v>
@@ -6903,37 +6903,37 @@
         <v>49.35</v>
       </c>
       <c r="M67">
-        <v>118.370421</v>
+        <v>120.1915044</v>
       </c>
       <c r="N67">
-        <v>-69.020421</v>
+        <v>-70.84150440000002</v>
       </c>
       <c r="O67">
-        <v>-13.8040842</v>
+        <v>-14.16830088</v>
       </c>
       <c r="P67">
-        <v>-55.2163368</v>
+        <v>-56.67320352000002</v>
       </c>
       <c r="Q67">
-        <v>-41.3163368</v>
+        <v>-42.77320352000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1380312271175154</v>
+        <v>0.1407439102680306</v>
       </c>
       <c r="T67">
-        <v>1.797758286413133</v>
+        <v>1.850633530131166</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08338231727671223</v>
+        <v>0.08211894883312568</v>
       </c>
       <c r="W67">
-        <v>0.2161384495861513</v>
+        <v>0.216436351865149</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4169115863835612</v>
+        <v>0.4105947441656284</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1907009217221287</v>
+        <v>0.1926009217221287</v>
       </c>
       <c r="C68">
-        <v>-326.4749375447953</v>
+        <v>-336.4907761367899</v>
       </c>
       <c r="D68">
-        <v>177.1530624552047</v>
+        <v>174.8602238632101</v>
       </c>
       <c r="E68">
-        <v>376.218</v>
+        <v>383.941</v>
       </c>
       <c r="F68">
-        <v>509.718</v>
+        <v>517.441</v>
       </c>
       <c r="G68">
         <v>6.09</v>
@@ -6985,37 +6985,37 @@
         <v>49.35</v>
       </c>
       <c r="M68">
-        <v>120.1915044</v>
+        <v>122.0125878</v>
       </c>
       <c r="N68">
-        <v>-70.84150440000002</v>
+        <v>-72.66258780000001</v>
       </c>
       <c r="O68">
-        <v>-14.16830088</v>
+        <v>-14.53251756</v>
       </c>
       <c r="P68">
-        <v>-56.67320352000002</v>
+        <v>-58.13007024000001</v>
       </c>
       <c r="Q68">
-        <v>-42.77320352000002</v>
+        <v>-44.23007024000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1407439102680306</v>
+        <v>0.1436209984579709</v>
       </c>
       <c r="T68">
-        <v>1.850633530131166</v>
+        <v>1.906713334074535</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08211894883312568</v>
+        <v>0.08089329288039247</v>
       </c>
       <c r="W68">
-        <v>0.216436351865149</v>
+        <v>0.2167253615388035</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4105947441656284</v>
+        <v>0.4044664644019622</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1926009217221287</v>
+        <v>0.1945009217221287</v>
       </c>
       <c r="C69">
-        <v>-336.4907761367899</v>
+        <v>-346.4480220412029</v>
       </c>
       <c r="D69">
-        <v>174.8602238632101</v>
+        <v>172.6259779587971</v>
       </c>
       <c r="E69">
-        <v>383.941</v>
+        <v>391.664</v>
       </c>
       <c r="F69">
-        <v>517.441</v>
+        <v>525.164</v>
       </c>
       <c r="G69">
         <v>6.09</v>
@@ -7067,37 +7067,37 @@
         <v>49.35</v>
       </c>
       <c r="M69">
-        <v>122.0125878</v>
+        <v>123.8336712</v>
       </c>
       <c r="N69">
-        <v>-72.66258780000001</v>
+        <v>-74.4836712</v>
       </c>
       <c r="O69">
-        <v>-14.53251756</v>
+        <v>-14.89673424</v>
       </c>
       <c r="P69">
-        <v>-58.13007024000001</v>
+        <v>-59.58693696</v>
       </c>
       <c r="Q69">
-        <v>-44.23007024000001</v>
+        <v>-45.68693696</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1436209984579709</v>
+        <v>0.1466779046597825</v>
       </c>
       <c r="T69">
-        <v>1.906713334074535</v>
+        <v>1.966298125764365</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08089329288039247</v>
+        <v>0.07970368563215141</v>
       </c>
       <c r="W69">
-        <v>0.2167253615388035</v>
+        <v>0.2170058709279387</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4044664644019622</v>
+        <v>0.3985184281607569</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1945009217221287</v>
+        <v>0.1964009217221287</v>
       </c>
       <c r="C70">
-        <v>-346.4480220412029</v>
+        <v>-356.3488928959836</v>
       </c>
       <c r="D70">
-        <v>172.6259779587971</v>
+        <v>170.4481071040165</v>
       </c>
       <c r="E70">
-        <v>391.664</v>
+        <v>399.3870000000001</v>
       </c>
       <c r="F70">
-        <v>525.164</v>
+        <v>532.8870000000001</v>
       </c>
       <c r="G70">
         <v>6.09</v>
@@ -7149,37 +7149,37 @@
         <v>49.35</v>
       </c>
       <c r="M70">
-        <v>123.8336712</v>
+        <v>125.6547546</v>
       </c>
       <c r="N70">
-        <v>-74.4836712</v>
+        <v>-76.30475460000002</v>
       </c>
       <c r="O70">
-        <v>-14.89673424</v>
+        <v>-15.26095092000001</v>
       </c>
       <c r="P70">
-        <v>-59.58693696</v>
+        <v>-61.04380368000002</v>
       </c>
       <c r="Q70">
-        <v>-45.68693696</v>
+        <v>-47.14380368000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1466779046597825</v>
+        <v>0.1499320306165497</v>
       </c>
       <c r="T70">
-        <v>1.966298125764365</v>
+        <v>2.029727097563215</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07970368563215141</v>
+        <v>0.07854855975342456</v>
       </c>
       <c r="W70">
-        <v>0.2170058709279387</v>
+        <v>0.2172782496101425</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3985184281607569</v>
+        <v>0.3927427987671227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1964009217221287</v>
+        <v>0.1983009217221287</v>
       </c>
       <c r="C71">
-        <v>-356.3488928959836</v>
+        <v>-366.1954958213987</v>
       </c>
       <c r="D71">
-        <v>170.4481071040165</v>
+        <v>168.3245041786013</v>
       </c>
       <c r="E71">
-        <v>399.3870000000001</v>
+        <v>407.11</v>
       </c>
       <c r="F71">
-        <v>532.8870000000001</v>
+        <v>540.61</v>
       </c>
       <c r="G71">
         <v>6.09</v>
@@ -7231,37 +7231,37 @@
         <v>49.35</v>
       </c>
       <c r="M71">
-        <v>125.6547546</v>
+        <v>127.475838</v>
       </c>
       <c r="N71">
-        <v>-76.30475460000002</v>
+        <v>-78.12583800000002</v>
       </c>
       <c r="O71">
-        <v>-15.26095092000001</v>
+        <v>-15.6251676</v>
       </c>
       <c r="P71">
-        <v>-61.04380368000002</v>
+        <v>-62.50067040000001</v>
       </c>
       <c r="Q71">
-        <v>-47.14380368000002</v>
+        <v>-48.60067040000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1499320306165497</v>
+        <v>0.153403098303768</v>
       </c>
       <c r="T71">
-        <v>2.029727097563215</v>
+        <v>2.097384667481989</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07854855975342456</v>
+        <v>0.07742643747123279</v>
       </c>
       <c r="W71">
-        <v>0.2172782496101425</v>
+        <v>0.2175428460442833</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3927427987671227</v>
+        <v>0.3871321873561638</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1983009217221287</v>
+        <v>0.2002009217221287</v>
       </c>
       <c r="C72">
-        <v>-366.1954958213987</v>
+        <v>-375.9898342199797</v>
       </c>
       <c r="D72">
-        <v>168.3245041786013</v>
+        <v>166.2531657800203</v>
       </c>
       <c r="E72">
-        <v>407.11</v>
+        <v>414.833</v>
       </c>
       <c r="F72">
-        <v>540.61</v>
+        <v>548.333</v>
       </c>
       <c r="G72">
         <v>6.09</v>
@@ -7313,37 +7313,37 @@
         <v>49.35</v>
       </c>
       <c r="M72">
-        <v>127.475838</v>
+        <v>129.2969214</v>
       </c>
       <c r="N72">
-        <v>-78.12583800000002</v>
+        <v>-79.94692140000001</v>
       </c>
       <c r="O72">
-        <v>-15.6251676</v>
+        <v>-15.98938428</v>
       </c>
       <c r="P72">
-        <v>-62.50067040000001</v>
+        <v>-63.95753712</v>
       </c>
       <c r="Q72">
-        <v>-48.60067040000001</v>
+        <v>-50.05753712000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.153403098303768</v>
+        <v>0.1571135499694152</v>
       </c>
       <c r="T72">
-        <v>2.097384667481989</v>
+        <v>2.169708276705506</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07742643747123279</v>
+        <v>0.07633592426741261</v>
       </c>
       <c r="W72">
-        <v>0.2175428460442833</v>
+        <v>0.2177999890577441</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3871321873561638</v>
+        <v>0.381679621337063</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2002009217221287</v>
+        <v>0.2021009217221287</v>
       </c>
       <c r="C73">
-        <v>-375.9898342199797</v>
+        <v>-385.7338140805054</v>
       </c>
       <c r="D73">
-        <v>166.2531657800203</v>
+        <v>164.2321859194945</v>
       </c>
       <c r="E73">
-        <v>414.833</v>
+        <v>422.5559999999999</v>
       </c>
       <c r="F73">
-        <v>548.333</v>
+        <v>556.0559999999999</v>
       </c>
       <c r="G73">
         <v>6.09</v>
@@ -7395,37 +7395,37 @@
         <v>49.35</v>
       </c>
       <c r="M73">
-        <v>129.2969214</v>
+        <v>131.1180048</v>
       </c>
       <c r="N73">
-        <v>-79.94692140000001</v>
+        <v>-81.7680048</v>
       </c>
       <c r="O73">
-        <v>-15.98938428</v>
+        <v>-16.35360096</v>
       </c>
       <c r="P73">
-        <v>-63.95753712</v>
+        <v>-65.41440384000001</v>
       </c>
       <c r="Q73">
-        <v>-50.05753712000001</v>
+        <v>-51.51440384000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1571135499694152</v>
+        <v>0.1610890338968943</v>
       </c>
       <c r="T73">
-        <v>2.169708276705505</v>
+        <v>2.247197858016416</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07633592426741261</v>
+        <v>0.07527570309703188</v>
       </c>
       <c r="W73">
-        <v>0.2177999890577441</v>
+        <v>0.2180499892097199</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.381679621337063</v>
+        <v>0.3763785154851593</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2021009217221287</v>
+        <v>0.2040009217221287</v>
       </c>
       <c r="C74">
-        <v>-385.7338140805054</v>
+        <v>-395.4292498277201</v>
       </c>
       <c r="D74">
-        <v>164.2321859194945</v>
+        <v>162.2597501722798</v>
       </c>
       <c r="E74">
-        <v>422.5559999999999</v>
+        <v>430.279</v>
       </c>
       <c r="F74">
-        <v>556.0559999999999</v>
+        <v>563.779</v>
       </c>
       <c r="G74">
         <v>6.09</v>
@@ -7477,37 +7477,37 @@
         <v>49.35</v>
       </c>
       <c r="M74">
-        <v>131.1180048</v>
+        <v>132.9390882</v>
       </c>
       <c r="N74">
-        <v>-81.7680048</v>
+        <v>-83.58908820000002</v>
       </c>
       <c r="O74">
-        <v>-16.35360096</v>
+        <v>-16.71781764</v>
       </c>
       <c r="P74">
-        <v>-65.41440384000001</v>
+        <v>-66.87127056000001</v>
       </c>
       <c r="Q74">
-        <v>-51.51440384000001</v>
+        <v>-52.97127056000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1610890338968943</v>
+        <v>0.1653589981152978</v>
       </c>
       <c r="T74">
-        <v>2.247197858016416</v>
+        <v>2.33042740831332</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07527570309703188</v>
+        <v>0.07424452908200403</v>
       </c>
       <c r="W74">
-        <v>0.2180499892097199</v>
+        <v>0.2182931400424634</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3763785154851593</v>
+        <v>0.3712226454100201</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2040009217221287</v>
+        <v>0.2059009217221287</v>
       </c>
       <c r="C75">
-        <v>-395.4292498277201</v>
+        <v>-405.0778697555205</v>
       </c>
       <c r="D75">
-        <v>162.2597501722798</v>
+        <v>160.3341302444795</v>
       </c>
       <c r="E75">
-        <v>430.279</v>
+        <v>438.002</v>
       </c>
       <c r="F75">
-        <v>563.779</v>
+        <v>571.502</v>
       </c>
       <c r="G75">
         <v>6.09</v>
@@ -7559,37 +7559,37 @@
         <v>49.35</v>
       </c>
       <c r="M75">
-        <v>132.9390882</v>
+        <v>134.7601716</v>
       </c>
       <c r="N75">
-        <v>-83.58908820000002</v>
+        <v>-85.41017160000001</v>
       </c>
       <c r="O75">
-        <v>-16.71781764</v>
+        <v>-17.08203432</v>
       </c>
       <c r="P75">
-        <v>-66.87127056000001</v>
+        <v>-68.32813728000001</v>
       </c>
       <c r="Q75">
-        <v>-52.97127056000001</v>
+        <v>-54.42813728000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1653589981152978</v>
+        <v>0.1699574211197323</v>
       </c>
       <c r="T75">
-        <v>2.33042740831332</v>
+        <v>2.420059231709986</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07424452908200403</v>
+        <v>0.07324122463494993</v>
       </c>
       <c r="W75">
-        <v>0.2182931400424634</v>
+        <v>0.2185297192310788</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3712226454100201</v>
+        <v>0.3662061231747495</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059009217221287</v>
+        <v>0.2078009217221287</v>
       </c>
       <c r="C76">
-        <v>-405.0778697555205</v>
+        <v>-414.68132107781</v>
       </c>
       <c r="D76">
-        <v>160.3341302444795</v>
+        <v>158.4536789221899</v>
       </c>
       <c r="E76">
-        <v>438.002</v>
+        <v>445.7249999999999</v>
       </c>
       <c r="F76">
-        <v>571.502</v>
+        <v>579.2249999999999</v>
       </c>
       <c r="G76">
         <v>6.09</v>
@@ -7641,37 +7641,37 @@
         <v>49.35</v>
       </c>
       <c r="M76">
-        <v>134.7601716</v>
+        <v>136.581255</v>
       </c>
       <c r="N76">
-        <v>-85.41017160000001</v>
+        <v>-87.23125499999998</v>
       </c>
       <c r="O76">
-        <v>-17.08203432</v>
+        <v>-17.446251</v>
       </c>
       <c r="P76">
-        <v>-68.32813728000001</v>
+        <v>-69.78500399999999</v>
       </c>
       <c r="Q76">
-        <v>-54.42813728000001</v>
+        <v>-55.88500399999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1699574211197323</v>
+        <v>0.1749237179645216</v>
       </c>
       <c r="T76">
-        <v>2.420059231709986</v>
+        <v>2.516861600978387</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07324122463494993</v>
+        <v>0.07226467497315062</v>
       </c>
       <c r="W76">
-        <v>0.2185297192310788</v>
+        <v>0.2187599896413311</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3662061231747495</v>
+        <v>0.3613233748657531</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2078009217221287</v>
+        <v>0.2097009217221287</v>
       </c>
       <c r="C77">
-        <v>-414.68132107781</v>
+        <v>-424.2411746280455</v>
       </c>
       <c r="D77">
-        <v>158.4536789221899</v>
+        <v>156.6168253719544</v>
       </c>
       <c r="E77">
-        <v>445.7249999999999</v>
+        <v>453.448</v>
       </c>
       <c r="F77">
-        <v>579.2249999999999</v>
+        <v>586.948</v>
       </c>
       <c r="G77">
         <v>6.09</v>
@@ -7723,37 +7723,37 @@
         <v>49.35</v>
       </c>
       <c r="M77">
-        <v>136.581255</v>
+        <v>138.4023384</v>
       </c>
       <c r="N77">
-        <v>-87.23125499999998</v>
+        <v>-89.0523384</v>
       </c>
       <c r="O77">
-        <v>-17.446251</v>
+        <v>-17.81046768</v>
       </c>
       <c r="P77">
-        <v>-69.78500399999999</v>
+        <v>-71.24187071999999</v>
       </c>
       <c r="Q77">
-        <v>-55.88500399999999</v>
+        <v>-57.34187072</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1749237179645216</v>
+        <v>0.18030387287971</v>
       </c>
       <c r="T77">
-        <v>2.516861600978387</v>
+        <v>2.621730834352486</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07226467497315062</v>
+        <v>0.07131382398666179</v>
       </c>
       <c r="W77">
-        <v>0.2187599896413311</v>
+        <v>0.2189842003039452</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3613233748657531</v>
+        <v>0.3565691199333089</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2097009217221287</v>
+        <v>0.2116009217221287</v>
       </c>
       <c r="C78">
-        <v>-424.2411746280455</v>
+        <v>-433.7589292356552</v>
       </c>
       <c r="D78">
-        <v>156.6168253719544</v>
+        <v>154.8220707643447</v>
       </c>
       <c r="E78">
-        <v>453.448</v>
+        <v>461.1709999999999</v>
       </c>
       <c r="F78">
-        <v>586.948</v>
+        <v>594.6709999999999</v>
       </c>
       <c r="G78">
         <v>6.09</v>
@@ -7805,37 +7805,37 @@
         <v>49.35</v>
       </c>
       <c r="M78">
-        <v>138.4023384</v>
+        <v>140.2234218</v>
       </c>
       <c r="N78">
-        <v>-89.0523384</v>
+        <v>-90.87342179999999</v>
       </c>
       <c r="O78">
-        <v>-17.81046768</v>
+        <v>-18.17468436</v>
       </c>
       <c r="P78">
-        <v>-71.24187071999999</v>
+        <v>-72.69873743999999</v>
       </c>
       <c r="Q78">
-        <v>-57.34187072</v>
+        <v>-58.79873743999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.18030387287971</v>
+        <v>0.1861518673527409</v>
       </c>
       <c r="T78">
-        <v>2.621730834352486</v>
+        <v>2.735719131498247</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07131382398666179</v>
+        <v>0.07038767042839345</v>
       </c>
       <c r="W78">
-        <v>0.2189842003039452</v>
+        <v>0.2192025873129848</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3565691199333089</v>
+        <v>0.3519383521419672</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116009217221287</v>
+        <v>0.2135009217221287</v>
       </c>
       <c r="C79">
-        <v>-433.7589292356552</v>
+        <v>-443.2360158049567</v>
       </c>
       <c r="D79">
-        <v>154.8220707643447</v>
+        <v>153.0679841950434</v>
       </c>
       <c r="E79">
-        <v>461.1709999999999</v>
+        <v>468.894</v>
       </c>
       <c r="F79">
-        <v>594.6709999999999</v>
+        <v>602.394</v>
       </c>
       <c r="G79">
         <v>6.09</v>
@@ -7887,37 +7887,37 @@
         <v>49.35</v>
       </c>
       <c r="M79">
-        <v>140.2234218</v>
+        <v>142.0445052</v>
       </c>
       <c r="N79">
-        <v>-90.87342179999999</v>
+        <v>-92.69450520000001</v>
       </c>
       <c r="O79">
-        <v>-18.17468436</v>
+        <v>-18.53890104</v>
       </c>
       <c r="P79">
-        <v>-72.69873743999999</v>
+        <v>-74.15560416000001</v>
       </c>
       <c r="Q79">
-        <v>-58.79873743999999</v>
+        <v>-60.25560416000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1861518673527409</v>
+        <v>0.1925314976869564</v>
       </c>
       <c r="T79">
-        <v>2.735719131498247</v>
+        <v>2.860070001111803</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07038767042839345</v>
+        <v>0.0694852643972602</v>
       </c>
       <c r="W79">
-        <v>0.2192025873129848</v>
+        <v>0.2194153746551261</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3519383521419672</v>
+        <v>0.3474263219863009</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135009217221287</v>
+        <v>0.2154009217221287</v>
       </c>
       <c r="C80">
-        <v>-443.2360158049567</v>
+        <v>-452.6738011199036</v>
       </c>
       <c r="D80">
-        <v>153.0679841950434</v>
+        <v>151.3531988800964</v>
       </c>
       <c r="E80">
-        <v>468.894</v>
+        <v>476.617</v>
       </c>
       <c r="F80">
-        <v>602.394</v>
+        <v>610.117</v>
       </c>
       <c r="G80">
         <v>6.09</v>
@@ -7969,37 +7969,37 @@
         <v>49.35</v>
       </c>
       <c r="M80">
-        <v>142.0445052</v>
+        <v>143.8655886</v>
       </c>
       <c r="N80">
-        <v>-92.69450520000001</v>
+        <v>-94.5155886</v>
       </c>
       <c r="O80">
-        <v>-18.53890104</v>
+        <v>-18.90311772</v>
       </c>
       <c r="P80">
-        <v>-74.15560416000001</v>
+        <v>-75.61247088</v>
       </c>
       <c r="Q80">
-        <v>-60.25560416000001</v>
+        <v>-61.71247088000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1925314976869564</v>
+        <v>0.1995187118625257</v>
       </c>
       <c r="T80">
-        <v>2.860070001111803</v>
+        <v>2.996263810688556</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0694852643972602</v>
+        <v>0.06860570408843412</v>
       </c>
       <c r="W80">
-        <v>0.2194153746551261</v>
+        <v>0.2196227749759472</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3474263219863009</v>
+        <v>0.3430285204421706</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154009217221287</v>
+        <v>0.2173009217221287</v>
       </c>
       <c r="C81">
-        <v>-452.6738011199036</v>
+        <v>-462.073591395924</v>
       </c>
       <c r="D81">
-        <v>151.3531988800964</v>
+        <v>149.676408604076</v>
       </c>
       <c r="E81">
-        <v>476.617</v>
+        <v>484.34</v>
       </c>
       <c r="F81">
-        <v>610.117</v>
+        <v>617.84</v>
       </c>
       <c r="G81">
         <v>6.09</v>
@@ -8051,37 +8051,37 @@
         <v>49.35</v>
       </c>
       <c r="M81">
-        <v>143.8655886</v>
+        <v>145.686672</v>
       </c>
       <c r="N81">
-        <v>-94.5155886</v>
+        <v>-96.33667200000002</v>
       </c>
       <c r="O81">
-        <v>-18.90311772</v>
+        <v>-19.26733440000001</v>
       </c>
       <c r="P81">
-        <v>-75.61247088</v>
+        <v>-77.06933760000001</v>
       </c>
       <c r="Q81">
-        <v>-61.71247088000001</v>
+        <v>-63.16933760000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1995187118625257</v>
+        <v>0.207204647455652</v>
       </c>
       <c r="T81">
-        <v>2.996263810688556</v>
+        <v>3.146077001222983</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06860570408843412</v>
+        <v>0.06774813278732869</v>
       </c>
       <c r="W81">
-        <v>0.2196227749759472</v>
+        <v>0.2198249902887479</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3430285204421706</v>
+        <v>0.3387406639366434</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2173009217221287</v>
+        <v>0.2192009217221287</v>
       </c>
       <c r="C82">
-        <v>-462.073591395924</v>
+        <v>-471.4366355982464</v>
       </c>
       <c r="D82">
-        <v>149.676408604076</v>
+        <v>148.0363644017536</v>
       </c>
       <c r="E82">
-        <v>484.34</v>
+        <v>492.063</v>
       </c>
       <c r="F82">
-        <v>617.84</v>
+        <v>625.563</v>
       </c>
       <c r="G82">
         <v>6.09</v>
@@ -8133,37 +8133,37 @@
         <v>49.35</v>
       </c>
       <c r="M82">
-        <v>145.686672</v>
+        <v>147.5077554</v>
       </c>
       <c r="N82">
-        <v>-96.33667200000002</v>
+        <v>-98.15775540000001</v>
       </c>
       <c r="O82">
-        <v>-19.26733440000001</v>
+        <v>-19.63155108</v>
       </c>
       <c r="P82">
-        <v>-77.06933760000001</v>
+        <v>-78.52620432000001</v>
       </c>
       <c r="Q82">
-        <v>-63.16933760000001</v>
+        <v>-64.62620432</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.207204647455652</v>
+        <v>0.2156996289006864</v>
       </c>
       <c r="T82">
-        <v>3.146077001222983</v>
+        <v>3.311660001287351</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06774813278732869</v>
+        <v>0.06691173608625055</v>
       </c>
       <c r="W82">
-        <v>0.2198249902887479</v>
+        <v>0.2200222126308621</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3387406639366434</v>
+        <v>0.3345586804312527</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2192009217221287</v>
+        <v>0.2211009217221288</v>
       </c>
       <c r="C83">
-        <v>-471.4366355982464</v>
+        <v>-480.764128544434</v>
       </c>
       <c r="D83">
-        <v>148.0363644017536</v>
+        <v>146.431871455566</v>
       </c>
       <c r="E83">
-        <v>492.063</v>
+        <v>499.7860000000001</v>
       </c>
       <c r="F83">
-        <v>625.563</v>
+        <v>633.2860000000001</v>
       </c>
       <c r="G83">
         <v>6.09</v>
@@ -8215,37 +8215,37 @@
         <v>49.35</v>
       </c>
       <c r="M83">
-        <v>147.5077554</v>
+        <v>149.3288388</v>
       </c>
       <c r="N83">
-        <v>-98.15775540000001</v>
+        <v>-99.97883880000003</v>
       </c>
       <c r="O83">
-        <v>-19.63155108</v>
+        <v>-19.99576776000001</v>
       </c>
       <c r="P83">
-        <v>-78.52620432000001</v>
+        <v>-79.98307104000003</v>
       </c>
       <c r="Q83">
-        <v>-64.62620432</v>
+        <v>-66.08307104000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2156996289006864</v>
+        <v>0.2251384971729467</v>
       </c>
       <c r="T83">
-        <v>3.311660001287351</v>
+        <v>3.495641112469982</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06691173608625055</v>
+        <v>0.0660957393047109</v>
       </c>
       <c r="W83">
-        <v>0.2200222126308621</v>
+        <v>0.2202146246719492</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3345586804312527</v>
+        <v>0.3304786965235544</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211009217221288</v>
+        <v>0.2230009217221287</v>
       </c>
       <c r="C84">
-        <v>-480.764128544434</v>
+        <v>-490.0572138073192</v>
       </c>
       <c r="D84">
-        <v>146.431871455566</v>
+        <v>144.8617861926809</v>
       </c>
       <c r="E84">
-        <v>499.7860000000001</v>
+        <v>507.509</v>
       </c>
       <c r="F84">
-        <v>633.2860000000001</v>
+        <v>641.009</v>
       </c>
       <c r="G84">
         <v>6.09</v>
@@ -8297,37 +8297,37 @@
         <v>49.35</v>
       </c>
       <c r="M84">
-        <v>149.3288388</v>
+        <v>151.1499222</v>
       </c>
       <c r="N84">
-        <v>-99.97883880000003</v>
+        <v>-101.7999222</v>
       </c>
       <c r="O84">
-        <v>-19.99576776000001</v>
+        <v>-20.35998444000001</v>
       </c>
       <c r="P84">
-        <v>-79.98307104000003</v>
+        <v>-81.43993776000002</v>
       </c>
       <c r="Q84">
-        <v>-66.08307104000002</v>
+        <v>-67.53993776000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2251384971729467</v>
+        <v>0.2356878205360612</v>
       </c>
       <c r="T84">
-        <v>3.495641112469982</v>
+        <v>3.701267060262334</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0660957393047109</v>
+        <v>0.06529940509622041</v>
       </c>
       <c r="W84">
-        <v>0.2202146246719492</v>
+        <v>0.2204024002783112</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3304786965235544</v>
+        <v>0.326497025481102</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2230009217221287</v>
+        <v>0.2249009217221287</v>
       </c>
       <c r="C85">
-        <v>-490.0572138073192</v>
+        <v>-499.3169864331636</v>
       </c>
       <c r="D85">
-        <v>144.8617861926809</v>
+        <v>143.3250135668363</v>
       </c>
       <c r="E85">
-        <v>507.509</v>
+        <v>515.232</v>
       </c>
       <c r="F85">
-        <v>641.009</v>
+        <v>648.732</v>
       </c>
       <c r="G85">
         <v>6.09</v>
@@ -8379,37 +8379,37 @@
         <v>49.35</v>
       </c>
       <c r="M85">
-        <v>151.1499222</v>
+        <v>152.9710056</v>
       </c>
       <c r="N85">
-        <v>-101.7999222</v>
+        <v>-103.6210056</v>
       </c>
       <c r="O85">
-        <v>-20.35998444000001</v>
+        <v>-20.72420112</v>
       </c>
       <c r="P85">
-        <v>-81.43993776000002</v>
+        <v>-82.89680448000001</v>
       </c>
       <c r="Q85">
-        <v>-67.53993776000002</v>
+        <v>-68.99680448000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2356878205360612</v>
+        <v>0.2475558093195651</v>
       </c>
       <c r="T85">
-        <v>3.701267060262334</v>
+        <v>3.93259625152873</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06529940509622041</v>
+        <v>0.06452203122602733</v>
       </c>
       <c r="W85">
-        <v>0.2204024002783112</v>
+        <v>0.2205857050369028</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.326497025481102</v>
+        <v>0.3226101561301365</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2249009217221287</v>
+        <v>0.2268009217221287</v>
       </c>
       <c r="C86">
-        <v>-499.3169864331635</v>
+        <v>-508.5444954886204</v>
       </c>
       <c r="D86">
-        <v>143.3250135668364</v>
+        <v>141.8205045113795</v>
       </c>
       <c r="E86">
-        <v>515.232</v>
+        <v>522.9549999999999</v>
       </c>
       <c r="F86">
-        <v>648.732</v>
+        <v>656.4549999999999</v>
       </c>
       <c r="G86">
         <v>6.09</v>
@@ -8461,37 +8461,37 @@
         <v>49.35</v>
       </c>
       <c r="M86">
-        <v>152.9710056</v>
+        <v>154.792089</v>
       </c>
       <c r="N86">
-        <v>-103.6210056</v>
+        <v>-105.442089</v>
       </c>
       <c r="O86">
-        <v>-20.72420112</v>
+        <v>-21.0884178</v>
       </c>
       <c r="P86">
-        <v>-82.89680448000001</v>
+        <v>-84.35367119999998</v>
       </c>
       <c r="Q86">
-        <v>-68.99680448000001</v>
+        <v>-70.45367119999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.247555809319565</v>
+        <v>0.2610061966075359</v>
       </c>
       <c r="T86">
-        <v>3.932596251528728</v>
+        <v>4.194769334963977</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06452203122602733</v>
+        <v>0.06376294850572113</v>
       </c>
       <c r="W86">
-        <v>0.2205857050369028</v>
+        <v>0.220764696742351</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3226101561301365</v>
+        <v>0.3188147425286056</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268009217221287</v>
+        <v>0.2287009217221287</v>
       </c>
       <c r="C87">
-        <v>-508.5444954886204</v>
+        <v>-517.7407464489464</v>
       </c>
       <c r="D87">
-        <v>141.8205045113795</v>
+        <v>140.3472535510535</v>
       </c>
       <c r="E87">
-        <v>522.9549999999999</v>
+        <v>530.678</v>
       </c>
       <c r="F87">
-        <v>656.4549999999999</v>
+        <v>664.178</v>
       </c>
       <c r="G87">
         <v>6.09</v>
@@ -8543,37 +8543,37 @@
         <v>49.35</v>
       </c>
       <c r="M87">
-        <v>154.792089</v>
+        <v>156.6131724</v>
       </c>
       <c r="N87">
-        <v>-105.442089</v>
+        <v>-107.2631724</v>
       </c>
       <c r="O87">
-        <v>-21.0884178</v>
+        <v>-21.45263448</v>
       </c>
       <c r="P87">
-        <v>-84.35367119999998</v>
+        <v>-85.81053792</v>
       </c>
       <c r="Q87">
-        <v>-70.45367119999997</v>
+        <v>-71.91053792</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2610061966075359</v>
+        <v>0.2763780677937885</v>
       </c>
       <c r="T87">
-        <v>4.194769334963977</v>
+        <v>4.494395716032832</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06376294850572113</v>
+        <v>0.06302151887193368</v>
       </c>
       <c r="W87">
-        <v>0.220764696742351</v>
+        <v>0.2209395258499981</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3188147425286056</v>
+        <v>0.3151075943596683</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2287009217221287</v>
+        <v>0.2306009217221287</v>
       </c>
       <c r="C88">
-        <v>-517.7407464489464</v>
+        <v>-526.9067034388902</v>
       </c>
       <c r="D88">
-        <v>140.3472535510535</v>
+        <v>138.9042965611097</v>
       </c>
       <c r="E88">
-        <v>530.678</v>
+        <v>538.401</v>
       </c>
       <c r="F88">
-        <v>664.178</v>
+        <v>671.901</v>
       </c>
       <c r="G88">
         <v>6.09</v>
@@ -8625,37 +8625,37 @@
         <v>49.35</v>
       </c>
       <c r="M88">
-        <v>156.6131724</v>
+        <v>158.4342558</v>
       </c>
       <c r="N88">
-        <v>-107.2631724</v>
+        <v>-109.0842558</v>
       </c>
       <c r="O88">
-        <v>-21.45263448</v>
+        <v>-21.81685116</v>
       </c>
       <c r="P88">
-        <v>-85.81053792</v>
+        <v>-87.26740464</v>
       </c>
       <c r="Q88">
-        <v>-71.91053792</v>
+        <v>-73.36740463999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2763780677937885</v>
+        <v>0.2941148422394645</v>
       </c>
       <c r="T88">
-        <v>4.494395716032832</v>
+        <v>4.840118463419973</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06302151887193368</v>
+        <v>0.06229713359754363</v>
       </c>
       <c r="W88">
-        <v>0.2209395258499981</v>
+        <v>0.2211103358976992</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3151075943596683</v>
+        <v>0.311485667987718</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2306009217221287</v>
+        <v>0.2325009217221287</v>
       </c>
       <c r="C89">
-        <v>-526.9067034388902</v>
+        <v>-536.0432913367523</v>
       </c>
       <c r="D89">
-        <v>138.9042965611097</v>
+        <v>137.4907086632476</v>
       </c>
       <c r="E89">
-        <v>538.401</v>
+        <v>546.1239999999999</v>
       </c>
       <c r="F89">
-        <v>671.901</v>
+        <v>679.6239999999999</v>
       </c>
       <c r="G89">
         <v>6.09</v>
@@ -8707,37 +8707,37 @@
         <v>49.35</v>
       </c>
       <c r="M89">
-        <v>158.4342558</v>
+        <v>160.2553392</v>
       </c>
       <c r="N89">
-        <v>-109.0842558</v>
+        <v>-110.9053392</v>
       </c>
       <c r="O89">
-        <v>-21.81685116</v>
+        <v>-22.18106784</v>
       </c>
       <c r="P89">
-        <v>-87.26740464</v>
+        <v>-88.72427135999999</v>
       </c>
       <c r="Q89">
-        <v>-73.36740463999999</v>
+        <v>-74.82427135999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2941148422394645</v>
+        <v>0.3148077457594201</v>
       </c>
       <c r="T89">
-        <v>4.840118463419973</v>
+        <v>5.243461668704972</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06229713359754363</v>
+        <v>0.06158921162484426</v>
       </c>
       <c r="W89">
-        <v>0.2211103358976992</v>
+        <v>0.2212772638988617</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.311485667987718</v>
+        <v>0.3079460581242213</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325009217221287</v>
+        <v>0.2344009217221287</v>
       </c>
       <c r="C90">
-        <v>-536.0432913367523</v>
+        <v>-545.1513977512643</v>
       </c>
       <c r="D90">
-        <v>137.4907086632476</v>
+        <v>136.1056022487357</v>
       </c>
       <c r="E90">
-        <v>546.1239999999999</v>
+        <v>553.847</v>
       </c>
       <c r="F90">
-        <v>679.6239999999999</v>
+        <v>687.347</v>
       </c>
       <c r="G90">
         <v>6.09</v>
@@ -8789,37 +8789,37 @@
         <v>49.35</v>
       </c>
       <c r="M90">
-        <v>160.2553392</v>
+        <v>162.0764226</v>
       </c>
       <c r="N90">
-        <v>-110.9053392</v>
+        <v>-112.7264226</v>
       </c>
       <c r="O90">
-        <v>-22.18106784</v>
+        <v>-22.54528452</v>
       </c>
       <c r="P90">
-        <v>-88.72427135999999</v>
+        <v>-90.18113808000001</v>
       </c>
       <c r="Q90">
-        <v>-74.82427135999998</v>
+        <v>-76.28113808000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3148077457594201</v>
+        <v>0.3392629953739127</v>
       </c>
       <c r="T90">
-        <v>5.243461668704972</v>
+        <v>5.720140002223606</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06158921162484426</v>
+        <v>0.06089719801108197</v>
       </c>
       <c r="W90">
-        <v>0.2212772638988617</v>
+        <v>0.2214404407089869</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3079460581242213</v>
+        <v>0.3044859900554098</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344009217221287</v>
+        <v>0.2363009217221287</v>
       </c>
       <c r="C91">
-        <v>-545.1513977512643</v>
+        <v>-554.2318748801665</v>
       </c>
       <c r="D91">
-        <v>136.1056022487357</v>
+        <v>134.7481251198335</v>
       </c>
       <c r="E91">
-        <v>553.847</v>
+        <v>561.5699999999999</v>
       </c>
       <c r="F91">
-        <v>687.347</v>
+        <v>695.0699999999999</v>
       </c>
       <c r="G91">
         <v>6.09</v>
@@ -8871,37 +8871,37 @@
         <v>49.35</v>
       </c>
       <c r="M91">
-        <v>162.0764226</v>
+        <v>163.897506</v>
       </c>
       <c r="N91">
-        <v>-112.7264226</v>
+        <v>-114.547506</v>
       </c>
       <c r="O91">
-        <v>-22.54528452</v>
+        <v>-22.9095012</v>
       </c>
       <c r="P91">
-        <v>-90.18113808000001</v>
+        <v>-91.6380048</v>
       </c>
       <c r="Q91">
-        <v>-76.28113808000001</v>
+        <v>-77.7380048</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3392629953739127</v>
+        <v>0.368609294911304</v>
       </c>
       <c r="T91">
-        <v>5.720140002223606</v>
+        <v>6.292154002445966</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06089719801108197</v>
+        <v>0.06022056247762551</v>
       </c>
       <c r="W91">
-        <v>0.2214404407089869</v>
+        <v>0.2215999913677759</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3044859900554098</v>
+        <v>0.3011028123881274</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2363009217221287</v>
+        <v>0.2382009217221287</v>
       </c>
       <c r="C92">
-        <v>-554.2318748801665</v>
+        <v>-563.2855412586646</v>
       </c>
       <c r="D92">
-        <v>134.7481251198335</v>
+        <v>133.4174587413354</v>
       </c>
       <c r="E92">
-        <v>561.5699999999999</v>
+        <v>569.293</v>
       </c>
       <c r="F92">
-        <v>695.0699999999999</v>
+        <v>702.793</v>
       </c>
       <c r="G92">
         <v>6.09</v>
@@ -8953,37 +8953,37 @@
         <v>49.35</v>
       </c>
       <c r="M92">
-        <v>163.897506</v>
+        <v>165.7185894</v>
       </c>
       <c r="N92">
-        <v>-114.547506</v>
+        <v>-116.3685894</v>
       </c>
       <c r="O92">
-        <v>-22.9095012</v>
+        <v>-23.27371788000001</v>
       </c>
       <c r="P92">
-        <v>-91.6380048</v>
+        <v>-93.09487152000001</v>
       </c>
       <c r="Q92">
-        <v>-77.7380048</v>
+        <v>-79.19487152000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.368609294911304</v>
+        <v>0.4044769943458934</v>
       </c>
       <c r="T92">
-        <v>6.292154002445966</v>
+        <v>6.991282224939964</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06022056247762551</v>
+        <v>0.05955879805479445</v>
       </c>
       <c r="W92">
-        <v>0.2215999913677759</v>
+        <v>0.2217560354186795</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3011028123881274</v>
+        <v>0.2977939902739722</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2382009217221287</v>
+        <v>0.2401009217221287</v>
       </c>
       <c r="C93">
-        <v>-563.2855412586646</v>
+        <v>-572.3131834052987</v>
       </c>
       <c r="D93">
-        <v>133.4174587413354</v>
+        <v>132.1128165947013</v>
       </c>
       <c r="E93">
-        <v>569.293</v>
+        <v>577.016</v>
       </c>
       <c r="F93">
-        <v>702.793</v>
+        <v>710.516</v>
       </c>
       <c r="G93">
         <v>6.09</v>
@@ -9035,37 +9035,37 @@
         <v>49.35</v>
       </c>
       <c r="M93">
-        <v>165.7185894</v>
+        <v>167.5396728</v>
       </c>
       <c r="N93">
-        <v>-116.3685894</v>
+        <v>-118.1896728</v>
       </c>
       <c r="O93">
-        <v>-23.27371788000001</v>
+        <v>-23.63793456000001</v>
       </c>
       <c r="P93">
-        <v>-93.09487152000001</v>
+        <v>-94.55173824000001</v>
       </c>
       <c r="Q93">
-        <v>-79.19487152000002</v>
+        <v>-80.65173824000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4044769943458934</v>
+        <v>0.4493116186391302</v>
       </c>
       <c r="T93">
-        <v>6.991282224939964</v>
+        <v>7.865192503057461</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05955879805479445</v>
+        <v>0.05891141981506842</v>
       </c>
       <c r="W93">
-        <v>0.2217560354186795</v>
+        <v>0.2219086872076069</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2977939902739722</v>
+        <v>0.2945570990753421</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2401009217221287</v>
+        <v>0.2420009217221287</v>
       </c>
       <c r="C94">
-        <v>-572.3131834052987</v>
+        <v>-581.3155573721828</v>
       </c>
       <c r="D94">
-        <v>132.1128165947013</v>
+        <v>130.8334426278173</v>
       </c>
       <c r="E94">
-        <v>577.016</v>
+        <v>584.739</v>
       </c>
       <c r="F94">
-        <v>710.516</v>
+        <v>718.239</v>
       </c>
       <c r="G94">
         <v>6.09</v>
@@ -9117,37 +9117,37 @@
         <v>49.35</v>
       </c>
       <c r="M94">
-        <v>167.5396728</v>
+        <v>169.3607562</v>
       </c>
       <c r="N94">
-        <v>-118.1896728</v>
+        <v>-120.0107562</v>
       </c>
       <c r="O94">
-        <v>-23.63793456000001</v>
+        <v>-24.00215124000001</v>
       </c>
       <c r="P94">
-        <v>-94.55173824000001</v>
+        <v>-96.00860496000003</v>
       </c>
       <c r="Q94">
-        <v>-80.65173824000001</v>
+        <v>-82.10860496000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4493116186391302</v>
+        <v>0.5069561355875774</v>
       </c>
       <c r="T94">
-        <v>7.865192503057461</v>
+        <v>8.988791432065671</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05891141981506842</v>
+        <v>0.05827796368802467</v>
       </c>
       <c r="W94">
-        <v>0.2219086872076069</v>
+        <v>0.2220580561623638</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2945570990753421</v>
+        <v>0.2913898184401233</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2420009217221287</v>
+        <v>0.2439009217221287</v>
       </c>
       <c r="C95">
-        <v>-581.3155573721828</v>
+        <v>-590.2933902060327</v>
       </c>
       <c r="D95">
-        <v>130.8334426278173</v>
+        <v>129.5786097939674</v>
       </c>
       <c r="E95">
-        <v>584.739</v>
+        <v>592.462</v>
       </c>
       <c r="F95">
-        <v>718.239</v>
+        <v>725.962</v>
       </c>
       <c r="G95">
         <v>6.09</v>
@@ -9199,37 +9199,37 @@
         <v>49.35</v>
       </c>
       <c r="M95">
-        <v>169.3607562</v>
+        <v>171.1818396</v>
       </c>
       <c r="N95">
-        <v>-120.0107562</v>
+        <v>-121.8318396</v>
       </c>
       <c r="O95">
-        <v>-24.00215124000001</v>
+        <v>-24.36636792000001</v>
       </c>
       <c r="P95">
-        <v>-96.00860496000003</v>
+        <v>-97.46547168000002</v>
       </c>
       <c r="Q95">
-        <v>-82.10860496000004</v>
+        <v>-83.56547168000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5069561355875774</v>
+        <v>0.5838154915188404</v>
       </c>
       <c r="T95">
-        <v>8.988791432065671</v>
+        <v>10.48692333740995</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05827796368802467</v>
+        <v>0.05765798535091803</v>
       </c>
       <c r="W95">
-        <v>0.2220580561623638</v>
+        <v>0.2222042470542535</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2913898184401233</v>
+        <v>0.2882899267545901</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2439009217221287</v>
+        <v>0.2458009217221287</v>
       </c>
       <c r="C96">
-        <v>-590.2933902060327</v>
+        <v>-599.2473813259165</v>
       </c>
       <c r="D96">
-        <v>129.5786097939674</v>
+        <v>128.3476186740835</v>
       </c>
       <c r="E96">
-        <v>592.462</v>
+        <v>600.1850000000001</v>
       </c>
       <c r="F96">
-        <v>725.962</v>
+        <v>733.6850000000001</v>
       </c>
       <c r="G96">
         <v>6.09</v>
@@ -9281,37 +9281,37 @@
         <v>49.35</v>
       </c>
       <c r="M96">
-        <v>171.1818396</v>
+        <v>173.002923</v>
       </c>
       <c r="N96">
-        <v>-121.8318396</v>
+        <v>-123.652923</v>
       </c>
       <c r="O96">
-        <v>-24.36636792000001</v>
+        <v>-24.7305846</v>
       </c>
       <c r="P96">
-        <v>-97.46547168000002</v>
+        <v>-98.92233840000002</v>
       </c>
       <c r="Q96">
-        <v>-83.56547168000003</v>
+        <v>-85.02233840000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5838154915188404</v>
+        <v>0.6914185898226087</v>
       </c>
       <c r="T96">
-        <v>10.48692333740995</v>
+        <v>12.58430800489195</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05765798535091803</v>
+        <v>0.05705105918932943</v>
       </c>
       <c r="W96">
-        <v>0.2222042470542535</v>
+        <v>0.2223473602431561</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2882899267545901</v>
+        <v>0.285255295946647</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2458009217221287</v>
+        <v>0.2477009217221287</v>
       </c>
       <c r="C97">
-        <v>-599.2473813259165</v>
+        <v>-608.1782038232125</v>
       </c>
       <c r="D97">
-        <v>128.3476186740835</v>
+        <v>127.1397961767876</v>
       </c>
       <c r="E97">
-        <v>600.1850000000001</v>
+        <v>607.908</v>
       </c>
       <c r="F97">
-        <v>733.6850000000001</v>
+        <v>741.408</v>
       </c>
       <c r="G97">
         <v>6.09</v>
@@ -9363,37 +9363,37 @@
         <v>49.35</v>
       </c>
       <c r="M97">
-        <v>173.002923</v>
+        <v>174.8240064</v>
       </c>
       <c r="N97">
-        <v>-123.652923</v>
+        <v>-125.4740064</v>
       </c>
       <c r="O97">
-        <v>-24.7305846</v>
+        <v>-25.09480128</v>
       </c>
       <c r="P97">
-        <v>-98.92233840000002</v>
+        <v>-100.37920512</v>
       </c>
       <c r="Q97">
-        <v>-85.02233840000002</v>
+        <v>-86.47920512000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6914185898226087</v>
+        <v>0.8528232372782614</v>
       </c>
       <c r="T97">
-        <v>12.58430800489195</v>
+        <v>15.73038500611494</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05705105918932943</v>
+        <v>0.05645677732277391</v>
       </c>
       <c r="W97">
-        <v>0.2223473602431561</v>
+        <v>0.2224874919072899</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.285255295946647</v>
+        <v>0.2822838866138695</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2477009217221287</v>
+        <v>0.2496009217221287</v>
       </c>
       <c r="C98">
-        <v>-608.1782038232122</v>
+        <v>-617.0865056888499</v>
       </c>
       <c r="D98">
-        <v>127.1397961767877</v>
+        <v>125.95449431115</v>
       </c>
       <c r="E98">
-        <v>607.9079999999999</v>
+        <v>615.631</v>
       </c>
       <c r="F98">
-        <v>741.4079999999999</v>
+        <v>749.131</v>
       </c>
       <c r="G98">
         <v>6.09</v>
@@ -9445,37 +9445,37 @@
         <v>49.35</v>
       </c>
       <c r="M98">
-        <v>174.8240064</v>
+        <v>176.6450898</v>
       </c>
       <c r="N98">
-        <v>-125.4740064</v>
+        <v>-127.2950898</v>
       </c>
       <c r="O98">
-        <v>-25.09480128</v>
+        <v>-25.45901796</v>
       </c>
       <c r="P98">
-        <v>-100.37920512</v>
+        <v>-101.83607184</v>
       </c>
       <c r="Q98">
-        <v>-86.47920511999999</v>
+        <v>-87.93607184000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8528232372782591</v>
+        <v>1.121830983037679</v>
       </c>
       <c r="T98">
-        <v>15.7303850061149</v>
+        <v>20.97384667481987</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05645677732277391</v>
+        <v>0.05587474869058037</v>
       </c>
       <c r="W98">
-        <v>0.2224874919072899</v>
+        <v>0.2226247342587611</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2822838866138695</v>
+        <v>0.2793737434529018</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2496009217221287</v>
+        <v>0.2515009217221287</v>
       </c>
       <c r="C99">
-        <v>-617.0865056888499</v>
+        <v>-625.9729109725387</v>
       </c>
       <c r="D99">
-        <v>125.95449431115</v>
+        <v>124.7910890274613</v>
       </c>
       <c r="E99">
-        <v>615.631</v>
+        <v>623.3539999999999</v>
       </c>
       <c r="F99">
-        <v>749.131</v>
+        <v>756.8539999999999</v>
       </c>
       <c r="G99">
         <v>6.09</v>
@@ -9527,37 +9527,37 @@
         <v>49.35</v>
       </c>
       <c r="M99">
-        <v>176.6450898</v>
+        <v>178.4661732</v>
       </c>
       <c r="N99">
-        <v>-127.2950898</v>
+        <v>-129.1161732</v>
       </c>
       <c r="O99">
-        <v>-25.45901796</v>
+        <v>-25.82323464</v>
       </c>
       <c r="P99">
-        <v>-101.83607184</v>
+        <v>-103.29293856</v>
       </c>
       <c r="Q99">
-        <v>-87.93607184000001</v>
+        <v>-89.39293856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.121830983037679</v>
+        <v>1.659846474556518</v>
       </c>
       <c r="T99">
-        <v>20.97384667481987</v>
+        <v>31.4607700122298</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05587474869058037</v>
+        <v>0.05530459819373771</v>
       </c>
       <c r="W99">
-        <v>0.2226247342587611</v>
+        <v>0.2227591757459167</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2793737434529018</v>
+        <v>0.2765229909686885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515009217221287</v>
+        <v>0.2534009217221287</v>
       </c>
       <c r="C100">
-        <v>-625.9729109725387</v>
+        <v>-634.8380208783393</v>
       </c>
       <c r="D100">
-        <v>124.7910890274613</v>
+        <v>123.6489791216607</v>
       </c>
       <c r="E100">
-        <v>623.3539999999999</v>
+        <v>631.077</v>
       </c>
       <c r="F100">
-        <v>756.8539999999999</v>
+        <v>764.577</v>
       </c>
       <c r="G100">
         <v>6.09</v>
@@ -9609,37 +9609,37 @@
         <v>49.35</v>
       </c>
       <c r="M100">
-        <v>178.4661732</v>
+        <v>180.2872566</v>
       </c>
       <c r="N100">
-        <v>-129.1161732</v>
+        <v>-130.9372566</v>
       </c>
       <c r="O100">
-        <v>-25.82323464</v>
+        <v>-26.18745132</v>
       </c>
       <c r="P100">
-        <v>-103.29293856</v>
+        <v>-104.74980528</v>
       </c>
       <c r="Q100">
-        <v>-89.39293856</v>
+        <v>-90.84980528</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.659846474556518</v>
+        <v>3.273892949113037</v>
       </c>
       <c r="T100">
-        <v>31.4607700122298</v>
+        <v>62.9215400244596</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05530459819373771</v>
+        <v>0.05474596588875045</v>
       </c>
       <c r="W100">
-        <v>0.2227591757459167</v>
+        <v>0.2228909012434326</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2765229909686885</v>
+        <v>0.2737298294437522</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2534009217221287</v>
-      </c>
-      <c r="C101">
-        <v>-634.8380208783393</v>
-      </c>
-      <c r="D101">
-        <v>123.6489791216607</v>
-      </c>
-      <c r="E101">
-        <v>631.077</v>
-      </c>
-      <c r="F101">
-        <v>764.577</v>
-      </c>
-      <c r="G101">
-        <v>6.09</v>
-      </c>
-      <c r="H101">
-        <v>638.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63.25</v>
-      </c>
-      <c r="K101">
-        <v>13.9</v>
-      </c>
-      <c r="L101">
-        <v>49.35</v>
-      </c>
-      <c r="M101">
-        <v>180.2872566</v>
-      </c>
-      <c r="N101">
-        <v>-130.9372566</v>
-      </c>
-      <c r="O101">
-        <v>-26.18745132</v>
-      </c>
-      <c r="P101">
-        <v>-104.74980528</v>
-      </c>
-      <c r="Q101">
-        <v>-90.84980528</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.273892949113037</v>
-      </c>
-      <c r="T101">
-        <v>62.9215400244596</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05474596588875045</v>
-      </c>
-      <c r="W101">
-        <v>0.2228909012434326</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2737298294437522</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
